--- a/results.xlsx
+++ b/results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\StarPublicSchool.edu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0C1AB789-08A8-49E2-B5E6-44AE7734FAC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA131F5C-F89F-4C5A-A267-FD2DBA8368B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1720" uniqueCount="549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1881" uniqueCount="684">
   <si>
     <t>Class</t>
   </si>
@@ -1669,19 +1669,430 @@
   </si>
   <si>
     <t>NURSERY-A</t>
+  </si>
+  <si>
+    <t>ASHIYANA KHATOON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOOR ALAM </t>
+  </si>
+  <si>
+    <t>SHAGUFTA KHATOON</t>
+  </si>
+  <si>
+    <t>SAMSUJOHA HASMI</t>
+  </si>
+  <si>
+    <t>CHAND BABU</t>
+  </si>
+  <si>
+    <t>MD SERAJ ANSARI</t>
+  </si>
+  <si>
+    <t>YAKUNDDIN ANSARI</t>
+  </si>
+  <si>
+    <t>IFRA KHATOON</t>
+  </si>
+  <si>
+    <t>JAMALUDDIN ALAM</t>
+  </si>
+  <si>
+    <t>FALAK ARA</t>
+  </si>
+  <si>
+    <t>WAKIL ANSARI</t>
+  </si>
+  <si>
+    <t>AASMA KHATOON</t>
+  </si>
+  <si>
+    <t>SHAKEEL ANSARI</t>
+  </si>
+  <si>
+    <t>JAGRITI PANDEY</t>
+  </si>
+  <si>
+    <t>RANJIT KUMAR PANDAY</t>
+  </si>
+  <si>
+    <t>KAMLUJAMA KHAN</t>
+  </si>
+  <si>
+    <t>ARADHYA KUMARI</t>
+  </si>
+  <si>
+    <t>SAJIYA KHATOON</t>
+  </si>
+  <si>
+    <t>MAHFUJ ALAM</t>
+  </si>
+  <si>
+    <t>AFSAR SHAH</t>
+  </si>
+  <si>
+    <t>REHANA KHATOON</t>
+  </si>
+  <si>
+    <t>SHEKH BAKHTIYAR</t>
+  </si>
+  <si>
+    <t>RAKIB ALI</t>
+  </si>
+  <si>
+    <t>HAIJAITULLAH KHAN</t>
+  </si>
+  <si>
+    <t>ARBAJ KHAN</t>
+  </si>
+  <si>
+    <t>FALAK PRAVEEN</t>
+  </si>
+  <si>
+    <t>SABBIR AHMAD</t>
+  </si>
+  <si>
+    <t>ATIF KHAN</t>
+  </si>
+  <si>
+    <t>AZAD KHAN</t>
+  </si>
+  <si>
+    <t>ANSHURAJ KUMAR</t>
+  </si>
+  <si>
+    <t>VIKASH YADAV</t>
+  </si>
+  <si>
+    <t>SURESH YADAV</t>
+  </si>
+  <si>
+    <t>FAIJAL KHAN</t>
+  </si>
+  <si>
+    <t>SAJJAD KHAN</t>
+  </si>
+  <si>
+    <t>NIGAHE NOOR</t>
+  </si>
+  <si>
+    <t>JUBAIR KHAN</t>
+  </si>
+  <si>
+    <t>FARID KHAN</t>
+  </si>
+  <si>
+    <t>ALI ANSARI</t>
+  </si>
+  <si>
+    <t>YAKINUDDIN ANSARI</t>
+  </si>
+  <si>
+    <t>TETRI KHATOON</t>
+  </si>
+  <si>
+    <t>KALAM KHAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AJIBULLAH </t>
+  </si>
+  <si>
+    <t>MUJIBULLAH MIYA</t>
+  </si>
+  <si>
+    <t>MANOJ YADAV</t>
+  </si>
+  <si>
+    <t>SAHANA KHATOON</t>
+  </si>
+  <si>
+    <t>MD MOMTAJ KHAN</t>
+  </si>
+  <si>
+    <t>M.D AYAN KHAN</t>
+  </si>
+  <si>
+    <t>WASIM SHEKH</t>
+  </si>
+  <si>
+    <t>MAHENOOR</t>
+  </si>
+  <si>
+    <t>YASH PANDEY</t>
+  </si>
+  <si>
+    <t>ESRANA KHATOON</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> MLALUDDIN MIYA</t>
+  </si>
+  <si>
+    <t>SANJANA KUMARI</t>
+  </si>
+  <si>
+    <t>BALAL SHAH</t>
+  </si>
+  <si>
+    <t>TAHIR SHAH</t>
+  </si>
+  <si>
+    <t>ABDUL AHAD</t>
+  </si>
+  <si>
+    <t>SHAHID AKBAL</t>
+  </si>
+  <si>
+    <t>KANHIYA KUMAR</t>
+  </si>
+  <si>
+    <t>DINESH YADAV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SHAHIL ALI </t>
+  </si>
+  <si>
+    <t>SALAUDDIN ANSARI</t>
+  </si>
+  <si>
+    <t>JAIRAM RAM SHARMA</t>
+  </si>
+  <si>
+    <t>ASHIF ANSARI</t>
+  </si>
+  <si>
+    <t>NAWED ANSARI</t>
+  </si>
+  <si>
+    <t>NADIM AHSAN</t>
+  </si>
+  <si>
+    <t>ASHOK KUMAR</t>
+  </si>
+  <si>
+    <t>GAJALA KHATOON</t>
+  </si>
+  <si>
+    <t>JAHANGIR KHAN</t>
+  </si>
+  <si>
+    <t>FARID ANSARI</t>
+  </si>
+  <si>
+    <t>BIRAL ANSARI</t>
+  </si>
+  <si>
+    <t>SAJAN KUMAR</t>
+  </si>
+  <si>
+    <t>SAFIYA KHATOON</t>
+  </si>
+  <si>
+    <t>ASIF KHAN</t>
+  </si>
+  <si>
+    <t>RIZWANULLAH KHAN</t>
+  </si>
+  <si>
+    <t>HALIMUN KHATOON</t>
+  </si>
+  <si>
+    <t>PANNALAL SAH</t>
+  </si>
+  <si>
+    <t>AYUSH KUMAR</t>
+  </si>
+  <si>
+    <t>SUGREEM GOND</t>
+  </si>
+  <si>
+    <t>ANJALI KUMARI</t>
+  </si>
+  <si>
+    <t>ABDUL KADIR</t>
+  </si>
+  <si>
+    <t>SABEER AHMAD</t>
+  </si>
+  <si>
+    <t>PRADEEP KUMAR</t>
+  </si>
+  <si>
+    <t>BHUWAL YADAV</t>
+  </si>
+  <si>
+    <t>SHAHIM ALAM</t>
+  </si>
+  <si>
+    <t>BUKAT MIYAN</t>
+  </si>
+  <si>
+    <t>ab</t>
+  </si>
+  <si>
+    <t>JUNAID SHAH</t>
+  </si>
+  <si>
+    <t>SARFRAZ SHAH</t>
+  </si>
+  <si>
+    <t>SURAJ KUMAR</t>
+  </si>
+  <si>
+    <t>SANTOSH GUPTA</t>
+  </si>
+  <si>
+    <t>ATIKA KHATOON</t>
+  </si>
+  <si>
+    <t>TAJUDDIN MIYAN</t>
+  </si>
+  <si>
+    <t>SOHAIL SHEKH</t>
+  </si>
+  <si>
+    <t>SHEKH ALIRAJ</t>
+  </si>
+  <si>
+    <t>SAIDUL ANSARI</t>
+  </si>
+  <si>
+    <t>JALAL ANSARI</t>
+  </si>
+  <si>
+    <t>ARIF ALAM</t>
+  </si>
+  <si>
+    <t>ARYAN KHAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> JUBBAIR KHAN</t>
+  </si>
+  <si>
+    <t>ABUHOJAIFA MIYAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SAJJAD MIYAN</t>
+  </si>
+  <si>
+    <t>ANURAG KUMAR</t>
+  </si>
+  <si>
+    <t>RAMACHANDRA GUPTA</t>
+  </si>
+  <si>
+    <t>ABUTALHA</t>
+  </si>
+  <si>
+    <t>ZAFAR AHMAD</t>
+  </si>
+  <si>
+    <t>JITENDRA YADAV</t>
+  </si>
+  <si>
+    <t>NASRAT ALI</t>
+  </si>
+  <si>
+    <t>ABDUL HAQUE</t>
+  </si>
+  <si>
+    <t>SHAHIL ANSARI</t>
+  </si>
+  <si>
+    <t>SALAUDDIN  MIYA</t>
+  </si>
+  <si>
+    <t>SHEKH SAMEER</t>
+  </si>
+  <si>
+    <t>KALAM SHEKH</t>
+  </si>
+  <si>
+    <t>TABSUMARA</t>
+  </si>
+  <si>
+    <t>JAVED AKHTAR</t>
+  </si>
+  <si>
+    <t>RASID AKBAL</t>
+  </si>
+  <si>
+    <t>QAMAR JAVED</t>
+  </si>
+  <si>
+    <t>ADIL KHAN</t>
+  </si>
+  <si>
+    <t>MD ABULLAH</t>
+  </si>
+  <si>
+    <t>KHESARI KUMAR</t>
+  </si>
+  <si>
+    <t>SANT YADAV</t>
+  </si>
+  <si>
+    <t>EHSAN ALI</t>
+  </si>
+  <si>
+    <t>JUAID SHAH</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> EKRAM ANSARI</t>
+  </si>
+  <si>
+    <t>DILSHAD ALAM</t>
+  </si>
+  <si>
+    <t>NAUSHAD ALAM</t>
+  </si>
+  <si>
+    <t>MAAZAMUL HAQUE</t>
+  </si>
+  <si>
+    <t>AASHIFA KHATOON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAHID ALI </t>
+  </si>
+  <si>
+    <t>CHIRAGUDDIN ANSARI</t>
+  </si>
+  <si>
+    <t>SUMIT KUMAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAHNAWAJ </t>
+  </si>
+  <si>
+    <t>MANMIT KUMAR</t>
+  </si>
+  <si>
+    <t>ISHAN HAIDAR</t>
+  </si>
+  <si>
+    <t>SIBBU KHAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MD. JAID </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1704,13 +2115,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2016,8 +2430,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q480"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:Q506"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="11.26953125" style="1" customWidth="1"/>
     <col min="2" max="2" width="8.7265625" style="1"/>
@@ -2036,7 +2450,7 @@
     <col min="18" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2089,7 +2503,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17">
       <c r="A2" s="1" t="s">
         <v>546</v>
       </c>
@@ -2100,7 +2514,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17">
       <c r="A3" s="1" t="s">
         <v>546</v>
       </c>
@@ -2112,7 +2526,7 @@
       </c>
       <c r="H3" s="2"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17">
       <c r="A4" s="1" t="s">
         <v>546</v>
       </c>
@@ -2150,7 +2564,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17">
       <c r="A5" s="1" t="s">
         <v>546</v>
       </c>
@@ -2191,7 +2605,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17">
       <c r="A6" s="1" t="s">
         <v>546</v>
       </c>
@@ -2203,7 +2617,7 @@
       </c>
       <c r="H6" s="2"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17">
       <c r="A7" s="1" t="s">
         <v>546</v>
       </c>
@@ -2244,7 +2658,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17">
       <c r="A8" s="1" t="s">
         <v>546</v>
       </c>
@@ -2256,7 +2670,7 @@
       </c>
       <c r="H8" s="2"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17">
       <c r="A9" s="1" t="s">
         <v>546</v>
       </c>
@@ -2294,7 +2708,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17">
       <c r="A10" s="1" t="s">
         <v>546</v>
       </c>
@@ -2306,7 +2720,7 @@
       </c>
       <c r="H10" s="2"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17">
       <c r="A11" s="1" t="s">
         <v>546</v>
       </c>
@@ -2318,7 +2732,7 @@
       </c>
       <c r="H11" s="2"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17">
       <c r="A12" s="1" t="s">
         <v>546</v>
       </c>
@@ -2359,7 +2773,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17">
       <c r="A13" s="1" t="s">
         <v>546</v>
       </c>
@@ -2371,7 +2785,7 @@
       </c>
       <c r="H13" s="2"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17">
       <c r="A14" s="1" t="s">
         <v>546</v>
       </c>
@@ -2412,7 +2826,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:17">
       <c r="A15" s="1" t="s">
         <v>546</v>
       </c>
@@ -2424,7 +2838,7 @@
       </c>
       <c r="H15" s="2"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17">
       <c r="A16" s="1" t="s">
         <v>546</v>
       </c>
@@ -2465,7 +2879,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:13">
       <c r="A17" s="1" t="s">
         <v>546</v>
       </c>
@@ -2477,7 +2891,7 @@
       </c>
       <c r="H17" s="2"/>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:13">
       <c r="A18" s="1" t="s">
         <v>546</v>
       </c>
@@ -2515,7 +2929,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:13">
       <c r="A19" s="1" t="s">
         <v>546</v>
       </c>
@@ -2556,7 +2970,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:13">
       <c r="A20" s="1" t="s">
         <v>546</v>
       </c>
@@ -2597,7 +3011,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:13">
       <c r="A21" s="1" t="s">
         <v>546</v>
       </c>
@@ -2638,7 +3052,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:13">
       <c r="A22" s="1" t="s">
         <v>546</v>
       </c>
@@ -2679,7 +3093,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:13">
       <c r="A23" s="1" t="s">
         <v>546</v>
       </c>
@@ -2717,7 +3131,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:13">
       <c r="A24" s="1" t="s">
         <v>546</v>
       </c>
@@ -2758,7 +3172,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:13">
       <c r="A25" s="1" t="s">
         <v>546</v>
       </c>
@@ -2796,7 +3210,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:13">
       <c r="A26" s="1" t="s">
         <v>546</v>
       </c>
@@ -2834,7 +3248,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:13">
       <c r="A27" s="1" t="s">
         <v>546</v>
       </c>
@@ -2875,7 +3289,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:13">
       <c r="A28" s="1" t="s">
         <v>546</v>
       </c>
@@ -2887,7 +3301,7 @@
       </c>
       <c r="H28" s="2"/>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:13">
       <c r="A29" s="1" t="s">
         <v>546</v>
       </c>
@@ -2899,7 +3313,7 @@
       </c>
       <c r="H29" s="2"/>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:13">
       <c r="A30" s="1" t="s">
         <v>546</v>
       </c>
@@ -2940,7 +3354,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:13">
       <c r="A31" s="1" t="s">
         <v>546</v>
       </c>
@@ -2951,7 +3365,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:13">
       <c r="A32" s="1" t="s">
         <v>546</v>
       </c>
@@ -2962,7 +3376,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:13">
       <c r="A33" s="1" t="s">
         <v>546</v>
       </c>
@@ -3003,7 +3417,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:13">
       <c r="A34" s="1" t="s">
         <v>546</v>
       </c>
@@ -3041,7 +3455,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:13">
       <c r="A35" s="1" t="s">
         <v>546</v>
       </c>
@@ -3082,7 +3496,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:13">
       <c r="A36" s="1" t="s">
         <v>546</v>
       </c>
@@ -3120,7 +3534,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:13">
       <c r="A37" s="1" t="s">
         <v>546</v>
       </c>
@@ -3161,7 +3575,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:13">
       <c r="A38" s="1" t="s">
         <v>546</v>
       </c>
@@ -3202,7 +3616,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:13">
       <c r="A39" s="1" t="s">
         <v>546</v>
       </c>
@@ -3243,7 +3657,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:13">
       <c r="A40" s="1" t="s">
         <v>546</v>
       </c>
@@ -3281,7 +3695,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:13">
       <c r="A41" s="1" t="s">
         <v>546</v>
       </c>
@@ -3319,7 +3733,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:13">
       <c r="A42" s="1" t="s">
         <v>546</v>
       </c>
@@ -3357,7 +3771,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:13">
       <c r="A43" s="1" t="s">
         <v>546</v>
       </c>
@@ -3395,7 +3809,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:13">
       <c r="A44" s="1" t="s">
         <v>546</v>
       </c>
@@ -3433,7 +3847,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:13">
       <c r="A47" s="1" t="s">
         <v>547</v>
       </c>
@@ -3474,7 +3888,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:13">
       <c r="A48" s="1" t="s">
         <v>547</v>
       </c>
@@ -3515,7 +3929,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:13">
       <c r="A49" s="1" t="s">
         <v>547</v>
       </c>
@@ -3556,7 +3970,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:13">
       <c r="A50" s="1" t="s">
         <v>547</v>
       </c>
@@ -3594,7 +4008,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:13">
       <c r="A51" s="1" t="s">
         <v>547</v>
       </c>
@@ -3632,7 +4046,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:13">
       <c r="A52" s="1" t="s">
         <v>547</v>
       </c>
@@ -3673,7 +4087,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:13">
       <c r="A53" s="1" t="s">
         <v>547</v>
       </c>
@@ -3711,7 +4125,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:13">
       <c r="A54" s="1" t="s">
         <v>547</v>
       </c>
@@ -3752,7 +4166,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:13">
       <c r="A55" s="1" t="s">
         <v>547</v>
       </c>
@@ -3790,7 +4204,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:13">
       <c r="A56" s="1" t="s">
         <v>547</v>
       </c>
@@ -3828,7 +4242,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:13">
       <c r="A57" s="1" t="s">
         <v>547</v>
       </c>
@@ -3869,7 +4283,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:13">
       <c r="A58" s="1" t="s">
         <v>547</v>
       </c>
@@ -3886,7 +4300,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:13">
       <c r="A59" s="1" t="s">
         <v>547</v>
       </c>
@@ -3927,7 +4341,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:13">
       <c r="A60" s="1" t="s">
         <v>547</v>
       </c>
@@ -3944,7 +4358,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:13">
       <c r="A61" s="1" t="s">
         <v>547</v>
       </c>
@@ -3985,7 +4399,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:13">
       <c r="A62" s="1" t="s">
         <v>547</v>
       </c>
@@ -4023,7 +4437,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:13">
       <c r="A63" s="1" t="s">
         <v>547</v>
       </c>
@@ -4061,7 +4475,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:13">
       <c r="A64" s="1" t="s">
         <v>547</v>
       </c>
@@ -4102,7 +4516,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:13">
       <c r="A65" s="1" t="s">
         <v>547</v>
       </c>
@@ -4143,7 +4557,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:13">
       <c r="A66" s="1" t="s">
         <v>547</v>
       </c>
@@ -4184,7 +4598,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:13">
       <c r="A67" s="1" t="s">
         <v>547</v>
       </c>
@@ -4225,7 +4639,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:13">
       <c r="A68" s="1" t="s">
         <v>547</v>
       </c>
@@ -4266,7 +4680,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:13">
       <c r="A69" s="1" t="s">
         <v>547</v>
       </c>
@@ -4307,7 +4721,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:13">
       <c r="A70" s="1" t="s">
         <v>547</v>
       </c>
@@ -4342,7 +4756,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:13">
       <c r="A71" s="1" t="s">
         <v>547</v>
       </c>
@@ -4380,7 +4794,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:13">
       <c r="A72" s="1" t="s">
         <v>547</v>
       </c>
@@ -4418,7 +4832,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:13">
       <c r="A73" s="1" t="s">
         <v>547</v>
       </c>
@@ -4456,7 +4870,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:13">
       <c r="A74" s="1" t="s">
         <v>547</v>
       </c>
@@ -4497,7 +4911,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:13">
       <c r="A75" s="1" t="s">
         <v>547</v>
       </c>
@@ -4538,7 +4952,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:13">
       <c r="A76" s="1" t="s">
         <v>547</v>
       </c>
@@ -4579,7 +4993,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:13">
       <c r="A77" s="1" t="s">
         <v>547</v>
       </c>
@@ -4617,7 +5031,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:13">
       <c r="A78" s="1" t="s">
         <v>547</v>
       </c>
@@ -4655,7 +5069,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:13">
       <c r="H79" s="1" t="s">
         <v>16</v>
       </c>
@@ -4663,7 +5077,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:13">
       <c r="A80" s="1" t="s">
         <v>548</v>
       </c>
@@ -4701,7 +5115,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:13">
       <c r="A81" s="1" t="s">
         <v>548</v>
       </c>
@@ -4742,7 +5156,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:13">
       <c r="A82" s="1" t="s">
         <v>548</v>
       </c>
@@ -4780,7 +5194,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:13">
       <c r="A83" s="1" t="s">
         <v>548</v>
       </c>
@@ -4797,7 +5211,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:13">
       <c r="A84" s="1" t="s">
         <v>548</v>
       </c>
@@ -4838,7 +5252,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:13">
       <c r="A85" s="1" t="s">
         <v>548</v>
       </c>
@@ -4879,7 +5293,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:13">
       <c r="A86" s="1" t="s">
         <v>548</v>
       </c>
@@ -4920,7 +5334,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:13">
       <c r="A87" s="1" t="s">
         <v>548</v>
       </c>
@@ -4961,7 +5375,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:13">
       <c r="A88" s="1" t="s">
         <v>548</v>
       </c>
@@ -5002,7 +5416,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:13">
       <c r="A89" s="1" t="s">
         <v>548</v>
       </c>
@@ -5043,7 +5457,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:13">
       <c r="A90" s="1" t="s">
         <v>548</v>
       </c>
@@ -5084,7 +5498,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:13">
       <c r="A91" s="1" t="s">
         <v>548</v>
       </c>
@@ -5101,7 +5515,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:13">
       <c r="A92" s="1" t="s">
         <v>548</v>
       </c>
@@ -5142,7 +5556,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:13">
       <c r="A93" s="1" t="s">
         <v>548</v>
       </c>
@@ -5180,7 +5594,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:13">
       <c r="A94" s="1" t="s">
         <v>548</v>
       </c>
@@ -5197,7 +5611,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:13">
       <c r="A95" s="1" t="s">
         <v>548</v>
       </c>
@@ -5238,7 +5652,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:13">
       <c r="A96" s="1" t="s">
         <v>548</v>
       </c>
@@ -5279,7 +5693,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:13">
       <c r="A97" s="1" t="s">
         <v>548</v>
       </c>
@@ -5320,7 +5734,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:13">
       <c r="A98" s="1" t="s">
         <v>548</v>
       </c>
@@ -5361,7 +5775,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:13">
       <c r="A99" s="1" t="s">
         <v>548</v>
       </c>
@@ -5402,7 +5816,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:13">
       <c r="A100" s="1" t="s">
         <v>548</v>
       </c>
@@ -5440,7 +5854,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:13">
       <c r="A101" s="1" t="s">
         <v>548</v>
       </c>
@@ -5481,7 +5895,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:13">
       <c r="A102" s="1" t="s">
         <v>548</v>
       </c>
@@ -5522,7 +5936,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:13">
       <c r="A103" s="1" t="s">
         <v>548</v>
       </c>
@@ -5560,7 +5974,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:13">
       <c r="A104" s="1" t="s">
         <v>548</v>
       </c>
@@ -5598,7 +6012,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:13">
       <c r="A105" s="1" t="s">
         <v>548</v>
       </c>
@@ -5639,7 +6053,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:13">
       <c r="A106" s="1" t="s">
         <v>548</v>
       </c>
@@ -5677,7 +6091,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:13">
       <c r="A107" s="1" t="s">
         <v>548</v>
       </c>
@@ -5718,7 +6132,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:13">
       <c r="A108" s="1" t="s">
         <v>548</v>
       </c>
@@ -5756,7 +6170,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:13">
       <c r="A109" s="1" t="s">
         <v>548</v>
       </c>
@@ -5791,7 +6205,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:13">
       <c r="A110" s="1" t="s">
         <v>548</v>
       </c>
@@ -5832,7 +6246,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:13">
       <c r="A113" s="1" t="s">
         <v>297</v>
       </c>
@@ -5873,7 +6287,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:13">
       <c r="A114" s="1" t="s">
         <v>297</v>
       </c>
@@ -5914,7 +6328,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:13">
       <c r="A115" s="1" t="s">
         <v>297</v>
       </c>
@@ -5952,7 +6366,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:13">
       <c r="A116" s="1" t="s">
         <v>297</v>
       </c>
@@ -5993,7 +6407,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:13">
       <c r="A117" s="1" t="s">
         <v>297</v>
       </c>
@@ -6034,7 +6448,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:13">
       <c r="A118" s="1" t="s">
         <v>297</v>
       </c>
@@ -6075,7 +6489,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:13">
       <c r="A119" s="1" t="s">
         <v>297</v>
       </c>
@@ -6116,7 +6530,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:13">
       <c r="A120" s="1" t="s">
         <v>297</v>
       </c>
@@ -6157,7 +6571,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:13">
       <c r="A121" s="1" t="s">
         <v>297</v>
       </c>
@@ -6198,7 +6612,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:13">
       <c r="A122" s="1" t="s">
         <v>297</v>
       </c>
@@ -6239,7 +6653,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:13">
       <c r="A123" s="1" t="s">
         <v>297</v>
       </c>
@@ -6280,7 +6694,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:13">
       <c r="A124" s="1" t="s">
         <v>297</v>
       </c>
@@ -6321,7 +6735,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:13">
       <c r="A125" s="1" t="s">
         <v>297</v>
       </c>
@@ -6362,7 +6776,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:13">
       <c r="A126" s="1" t="s">
         <v>297</v>
       </c>
@@ -6403,7 +6817,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:13">
       <c r="A127" s="1" t="s">
         <v>297</v>
       </c>
@@ -6441,7 +6855,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:13">
       <c r="A128" s="1" t="s">
         <v>297</v>
       </c>
@@ -6479,7 +6893,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:13">
       <c r="A129" s="1" t="s">
         <v>297</v>
       </c>
@@ -6520,7 +6934,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:13">
       <c r="A130" s="1" t="s">
         <v>297</v>
       </c>
@@ -6561,7 +6975,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:13">
       <c r="A131" s="1" t="s">
         <v>297</v>
       </c>
@@ -6602,7 +7016,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:13">
       <c r="A132" s="1" t="s">
         <v>297</v>
       </c>
@@ -6643,7 +7057,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:13">
       <c r="A133" s="1" t="s">
         <v>297</v>
       </c>
@@ -6681,7 +7095,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:13">
       <c r="A134" s="1" t="s">
         <v>297</v>
       </c>
@@ -6722,7 +7136,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:13">
       <c r="A135" s="1" t="s">
         <v>297</v>
       </c>
@@ -6763,7 +7177,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:13">
       <c r="A136" s="1" t="s">
         <v>297</v>
       </c>
@@ -6804,7 +7218,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:13">
       <c r="A137" s="1" t="s">
         <v>297</v>
       </c>
@@ -6845,7 +7259,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:13">
       <c r="A138" s="1" t="s">
         <v>297</v>
       </c>
@@ -6886,7 +7300,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:13">
       <c r="A139" s="1" t="s">
         <v>297</v>
       </c>
@@ -6927,7 +7341,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:13">
       <c r="A140" s="1" t="s">
         <v>297</v>
       </c>
@@ -6968,7 +7382,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:13">
       <c r="A141" s="1" t="s">
         <v>297</v>
       </c>
@@ -7009,7 +7423,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:13">
       <c r="A142" s="1" t="s">
         <v>297</v>
       </c>
@@ -7050,7 +7464,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:13">
       <c r="A143" s="1" t="s">
         <v>297</v>
       </c>
@@ -7091,7 +7505,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:13">
       <c r="A144" s="1" t="s">
         <v>297</v>
       </c>
@@ -7132,7 +7546,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:13">
       <c r="A145" s="1" t="s">
         <v>297</v>
       </c>
@@ -7173,7 +7587,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:13">
       <c r="A146" s="1" t="s">
         <v>297</v>
       </c>
@@ -7190,7 +7604,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:13">
       <c r="A147" s="1" t="s">
         <v>297</v>
       </c>
@@ -7228,7 +7642,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:13">
       <c r="A148" s="1" t="s">
         <v>297</v>
       </c>
@@ -7269,7 +7683,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:13">
       <c r="A149" s="1" t="s">
         <v>297</v>
       </c>
@@ -7310,7 +7724,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:13">
       <c r="A150" s="1" t="s">
         <v>297</v>
       </c>
@@ -7348,7 +7762,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:13">
       <c r="A151" s="1" t="s">
         <v>297</v>
       </c>
@@ -7386,7 +7800,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:13">
       <c r="A154" s="1" t="s">
         <v>296</v>
       </c>
@@ -7427,7 +7841,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:13">
       <c r="A155" s="1" t="s">
         <v>296</v>
       </c>
@@ -7468,7 +7882,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:13">
       <c r="A156" s="1" t="s">
         <v>296</v>
       </c>
@@ -7509,7 +7923,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:13">
       <c r="A157" s="1" t="s">
         <v>296</v>
       </c>
@@ -7550,7 +7964,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:13">
       <c r="A158" s="1" t="s">
         <v>296</v>
       </c>
@@ -7591,7 +8005,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:13">
       <c r="A159" s="1" t="s">
         <v>296</v>
       </c>
@@ -7632,7 +8046,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:13">
       <c r="A160" s="1" t="s">
         <v>296</v>
       </c>
@@ -7670,7 +8084,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:13">
       <c r="A161" s="1" t="s">
         <v>296</v>
       </c>
@@ -7711,7 +8125,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:13">
       <c r="A162" s="1" t="s">
         <v>296</v>
       </c>
@@ -7752,7 +8166,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:13">
       <c r="A163" s="1" t="s">
         <v>296</v>
       </c>
@@ -7790,7 +8204,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:13">
       <c r="A164" s="1" t="s">
         <v>296</v>
       </c>
@@ -7831,7 +8245,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:13">
       <c r="A165" s="1" t="s">
         <v>296</v>
       </c>
@@ -7872,7 +8286,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="166" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:13">
       <c r="A166" s="1" t="s">
         <v>296</v>
       </c>
@@ -7910,7 +8324,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:13">
       <c r="A167" s="1" t="s">
         <v>296</v>
       </c>
@@ -7951,7 +8365,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:13">
       <c r="A168" s="1" t="s">
         <v>296</v>
       </c>
@@ -7992,7 +8406,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:13">
       <c r="A169" s="1" t="s">
         <v>296</v>
       </c>
@@ -8033,7 +8447,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:13">
       <c r="A170" s="1" t="s">
         <v>296</v>
       </c>
@@ -8074,7 +8488,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:13">
       <c r="A171" s="1" t="s">
         <v>296</v>
       </c>
@@ -8115,7 +8529,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:13">
       <c r="A172" s="1" t="s">
         <v>296</v>
       </c>
@@ -8156,7 +8570,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:13">
       <c r="A173" s="1" t="s">
         <v>296</v>
       </c>
@@ -8197,7 +8611,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:13">
       <c r="A174" s="1" t="s">
         <v>296</v>
       </c>
@@ -8238,7 +8652,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:13">
       <c r="A175" s="1" t="s">
         <v>296</v>
       </c>
@@ -8279,7 +8693,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:13">
       <c r="A176" s="1" t="s">
         <v>296</v>
       </c>
@@ -8320,7 +8734,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:13">
       <c r="A177" s="1" t="s">
         <v>296</v>
       </c>
@@ -8361,7 +8775,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:13">
       <c r="A178" s="1" t="s">
         <v>296</v>
       </c>
@@ -8402,7 +8816,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:13">
       <c r="A179" s="1" t="s">
         <v>296</v>
       </c>
@@ -8443,7 +8857,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:13">
       <c r="A180" s="1" t="s">
         <v>296</v>
       </c>
@@ -8481,7 +8895,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="181" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:13">
       <c r="A181" s="1" t="s">
         <v>296</v>
       </c>
@@ -8519,7 +8933,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="182" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:13">
       <c r="A182" s="1" t="s">
         <v>296</v>
       </c>
@@ -8560,7 +8974,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="185" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:13">
       <c r="A185" s="1" t="s">
         <v>295</v>
       </c>
@@ -8601,7 +9015,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:13">
       <c r="A186" s="1" t="s">
         <v>295</v>
       </c>
@@ -8642,7 +9056,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:13">
       <c r="A187" s="1" t="s">
         <v>295</v>
       </c>
@@ -8683,7 +9097,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="188" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:13">
       <c r="A188" s="1" t="s">
         <v>295</v>
       </c>
@@ -8724,7 +9138,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:13">
       <c r="A189" s="1" t="s">
         <v>295</v>
       </c>
@@ -8765,7 +9179,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:13">
       <c r="A190" s="1" t="s">
         <v>295</v>
       </c>
@@ -8806,7 +9220,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="191" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:13">
       <c r="A191" s="1" t="s">
         <v>295</v>
       </c>
@@ -8847,7 +9261,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="192" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:13">
       <c r="A192" s="1" t="s">
         <v>295</v>
       </c>
@@ -8888,7 +9302,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="193" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:13">
       <c r="A193" s="1" t="s">
         <v>295</v>
       </c>
@@ -8929,7 +9343,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="194" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:13">
       <c r="A194" s="1" t="s">
         <v>295</v>
       </c>
@@ -8970,7 +9384,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="195" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:13">
       <c r="A195" s="1" t="s">
         <v>295</v>
       </c>
@@ -9011,7 +9425,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="196" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:13">
       <c r="A196" s="1" t="s">
         <v>295</v>
       </c>
@@ -9052,7 +9466,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="197" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:13">
       <c r="A197" s="1" t="s">
         <v>295</v>
       </c>
@@ -9090,7 +9504,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="198" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:13">
       <c r="A198" s="1" t="s">
         <v>295</v>
       </c>
@@ -9131,7 +9545,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="199" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:13">
       <c r="A199" s="1" t="s">
         <v>295</v>
       </c>
@@ -9172,7 +9586,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="200" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:13">
       <c r="A200" s="1" t="s">
         <v>295</v>
       </c>
@@ -9213,7 +9627,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="201" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:13">
       <c r="A201" s="1" t="s">
         <v>295</v>
       </c>
@@ -9251,7 +9665,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="202" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:13">
       <c r="A202" s="1" t="s">
         <v>295</v>
       </c>
@@ -9289,7 +9703,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="203" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:13">
       <c r="A203" s="1" t="s">
         <v>295</v>
       </c>
@@ -9330,7 +9744,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="204" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:13">
       <c r="A204" s="1" t="s">
         <v>295</v>
       </c>
@@ -9371,7 +9785,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="205" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:13">
       <c r="A205" s="1" t="s">
         <v>295</v>
       </c>
@@ -9412,7 +9826,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="206" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:13">
       <c r="A206" s="1" t="s">
         <v>295</v>
       </c>
@@ -9453,7 +9867,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="207" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:13">
       <c r="A207" s="1" t="s">
         <v>295</v>
       </c>
@@ -9494,7 +9908,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="208" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:13">
       <c r="A208" s="1" t="s">
         <v>295</v>
       </c>
@@ -9535,7 +9949,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:13">
       <c r="A209" s="1" t="s">
         <v>295</v>
       </c>
@@ -9573,7 +9987,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:13">
       <c r="A210" s="1" t="s">
         <v>295</v>
       </c>
@@ -9614,7 +10028,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="211" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:13">
       <c r="A211" s="1" t="s">
         <v>295</v>
       </c>
@@ -9655,7 +10069,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="212" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:13">
       <c r="A212" s="1" t="s">
         <v>295</v>
       </c>
@@ -9696,7 +10110,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:13">
       <c r="A213" s="1" t="s">
         <v>295</v>
       </c>
@@ -9737,7 +10151,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:13">
       <c r="A214" s="1" t="s">
         <v>295</v>
       </c>
@@ -9778,7 +10192,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="215" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:13">
       <c r="A215" s="1" t="s">
         <v>295</v>
       </c>
@@ -9816,7 +10230,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="216" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:13">
       <c r="A216" s="1" t="s">
         <v>295</v>
       </c>
@@ -9854,7 +10268,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:13">
       <c r="A217" s="1" t="s">
         <v>295</v>
       </c>
@@ -9895,7 +10309,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:13">
       <c r="A218" s="1" t="s">
         <v>295</v>
       </c>
@@ -9933,7 +10347,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:13">
       <c r="A219" s="1" t="s">
         <v>295</v>
       </c>
@@ -9971,12 +10385,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:13">
       <c r="H221" s="1" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:13">
       <c r="A222" s="1" t="s">
         <v>294</v>
       </c>
@@ -9993,7 +10407,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:13">
       <c r="A223" s="1" t="s">
         <v>294</v>
       </c>
@@ -10034,7 +10448,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:13">
       <c r="A224" s="1" t="s">
         <v>294</v>
       </c>
@@ -10075,7 +10489,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="225" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:13">
       <c r="A225" s="1" t="s">
         <v>294</v>
       </c>
@@ -10116,7 +10530,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="226" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:13">
       <c r="A226" s="1" t="s">
         <v>294</v>
       </c>
@@ -10157,7 +10571,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="227" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:13">
       <c r="A227" s="1" t="s">
         <v>294</v>
       </c>
@@ -10198,7 +10612,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="228" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:13">
       <c r="A228" s="1" t="s">
         <v>294</v>
       </c>
@@ -10215,7 +10629,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="229" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:13">
       <c r="A229" s="1" t="s">
         <v>294</v>
       </c>
@@ -10256,7 +10670,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="230" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:13">
       <c r="A230" s="1" t="s">
         <v>294</v>
       </c>
@@ -10297,7 +10711,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="231" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:13">
       <c r="A231" s="1" t="s">
         <v>294</v>
       </c>
@@ -10338,7 +10752,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="232" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:13">
       <c r="A232" s="1" t="s">
         <v>294</v>
       </c>
@@ -10379,7 +10793,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="233" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:13">
       <c r="A233" s="1" t="s">
         <v>294</v>
       </c>
@@ -10420,7 +10834,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="234" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:13">
       <c r="A234" s="1" t="s">
         <v>294</v>
       </c>
@@ -10461,7 +10875,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="235" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:13">
       <c r="A235" s="1" t="s">
         <v>294</v>
       </c>
@@ -10502,7 +10916,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="236" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:13">
       <c r="A236" s="1" t="s">
         <v>294</v>
       </c>
@@ -10543,7 +10957,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="237" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:13">
       <c r="A237" s="1" t="s">
         <v>294</v>
       </c>
@@ -10560,7 +10974,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="238" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:13">
       <c r="A238" s="1" t="s">
         <v>294</v>
       </c>
@@ -10601,7 +11015,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="239" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:13">
       <c r="A239" s="1" t="s">
         <v>294</v>
       </c>
@@ -10639,7 +11053,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="240" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:13">
       <c r="A240" s="1" t="s">
         <v>294</v>
       </c>
@@ -10680,7 +11094,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="241" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:13">
       <c r="A241" s="1" t="s">
         <v>294</v>
       </c>
@@ -10721,7 +11135,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="242" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:13">
       <c r="A242" s="1" t="s">
         <v>294</v>
       </c>
@@ -10762,7 +11176,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="243" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:13">
       <c r="A243" s="1" t="s">
         <v>294</v>
       </c>
@@ -10803,7 +11217,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="244" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:13">
       <c r="A244" s="1" t="s">
         <v>294</v>
       </c>
@@ -10820,7 +11234,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="245" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:13">
       <c r="A245" s="1" t="s">
         <v>294</v>
       </c>
@@ -10861,7 +11275,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="246" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:13">
       <c r="A246" s="1" t="s">
         <v>294</v>
       </c>
@@ -10902,7 +11316,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="247" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:13">
       <c r="A247" s="1" t="s">
         <v>294</v>
       </c>
@@ -10940,7 +11354,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="248" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:13">
       <c r="A248" s="1" t="s">
         <v>294</v>
       </c>
@@ -10981,7 +11395,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="249" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:13">
       <c r="A249" s="1" t="s">
         <v>294</v>
       </c>
@@ -11022,7 +11436,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="250" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:13">
       <c r="A250" s="1" t="s">
         <v>294</v>
       </c>
@@ -11060,7 +11474,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="251" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:13">
       <c r="A251" s="1" t="s">
         <v>294</v>
       </c>
@@ -11098,7 +11512,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="252" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:13">
       <c r="A252" s="1" t="s">
         <v>294</v>
       </c>
@@ -11115,7 +11529,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="253" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:13">
       <c r="A253" s="1" t="s">
         <v>294</v>
       </c>
@@ -11153,7 +11567,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="254" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:13">
       <c r="A254" s="1" t="s">
         <v>252</v>
       </c>
@@ -11161,7 +11575,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="256" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:13">
       <c r="A256" s="1">
         <v>8</v>
       </c>
@@ -11202,7 +11616,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="257" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:13">
       <c r="A257" s="1">
         <v>8</v>
       </c>
@@ -11243,7 +11657,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="258" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:13">
       <c r="A258" s="1">
         <v>8</v>
       </c>
@@ -11284,7 +11698,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="259" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:13">
       <c r="A259" s="1">
         <v>8</v>
       </c>
@@ -11325,7 +11739,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="260" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:13">
       <c r="A260" s="1">
         <v>8</v>
       </c>
@@ -11366,7 +11780,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="261" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:13">
       <c r="A261" s="1">
         <v>8</v>
       </c>
@@ -11407,7 +11821,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="262" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:13">
       <c r="A262" s="1">
         <v>8</v>
       </c>
@@ -11448,7 +11862,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="263" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:13">
       <c r="A263" s="1">
         <v>8</v>
       </c>
@@ -11489,7 +11903,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="264" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:13">
       <c r="A264" s="1">
         <v>8</v>
       </c>
@@ -11530,7 +11944,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="265" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:13">
       <c r="A265" s="1">
         <v>8</v>
       </c>
@@ -11571,12 +11985,12 @@
         <v>85</v>
       </c>
     </row>
-    <row r="266" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:13">
       <c r="A266" s="1" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="267" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:13">
       <c r="A267" s="1">
         <v>7</v>
       </c>
@@ -11617,7 +12031,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="268" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:13">
       <c r="A268" s="1">
         <v>7</v>
       </c>
@@ -11658,7 +12072,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="269" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:13">
       <c r="A269" s="1">
         <v>7</v>
       </c>
@@ -11699,7 +12113,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="270" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:13">
       <c r="A270" s="1">
         <v>7</v>
       </c>
@@ -11707,17 +12121,17 @@
         <v>4</v>
       </c>
     </row>
-    <row r="271" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:13">
       <c r="B271" s="1" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="272" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:13">
       <c r="B272" s="1" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="273" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:13">
       <c r="A273" s="1">
         <v>6</v>
       </c>
@@ -11758,7 +12172,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="274" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:13">
       <c r="A274" s="1">
         <v>6</v>
       </c>
@@ -11799,7 +12213,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="275" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:13">
       <c r="A275" s="1">
         <v>6</v>
       </c>
@@ -11840,7 +12254,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="276" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:13">
       <c r="A276" s="1">
         <v>6</v>
       </c>
@@ -11881,7 +12295,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="277" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:13">
       <c r="A277" s="1">
         <v>6</v>
       </c>
@@ -11922,7 +12336,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="278" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:13">
       <c r="A278" s="1">
         <v>6</v>
       </c>
@@ -11963,7 +12377,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="279" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:13">
       <c r="A279" s="1">
         <v>6</v>
       </c>
@@ -12004,7 +12418,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="280" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:13">
       <c r="A280" s="1">
         <v>6</v>
       </c>
@@ -12045,7 +12459,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="281" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:13">
       <c r="A281" s="1">
         <v>6</v>
       </c>
@@ -12086,7 +12500,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="282" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:13">
       <c r="A282" s="1">
         <v>6</v>
       </c>
@@ -12127,7 +12541,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="283" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:13">
       <c r="A283" s="1">
         <v>6</v>
       </c>
@@ -12168,7 +12582,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="284" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:13">
       <c r="A284" s="1">
         <v>6</v>
       </c>
@@ -12209,7 +12623,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="285" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:13">
       <c r="A285" s="1">
         <v>6</v>
       </c>
@@ -12250,7 +12664,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="286" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:13">
       <c r="A286" s="1">
         <v>6</v>
       </c>
@@ -12291,7 +12705,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="287" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:13">
       <c r="A287" s="1">
         <v>6</v>
       </c>
@@ -12332,7 +12746,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="288" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:13">
       <c r="A288" s="1">
         <v>6</v>
       </c>
@@ -12373,7 +12787,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="289" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:13">
       <c r="A289" s="1">
         <v>6</v>
       </c>
@@ -12414,7 +12828,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="290" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:13">
       <c r="A290" s="1" t="s">
         <v>272</v>
       </c>
@@ -12422,7 +12836,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="291" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:13">
       <c r="A291" s="1" t="s">
         <v>272</v>
       </c>
@@ -12430,7 +12844,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="292" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:13">
       <c r="A292" s="1">
         <v>5</v>
       </c>
@@ -12468,7 +12882,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="293" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:13">
       <c r="A293" s="1">
         <v>5</v>
       </c>
@@ -12506,7 +12920,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="294" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:13">
       <c r="A294" s="1">
         <v>5</v>
       </c>
@@ -12544,7 +12958,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="295" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:13">
       <c r="A295" s="1">
         <v>5</v>
       </c>
@@ -12582,7 +12996,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="296" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:13">
       <c r="A296" s="1">
         <v>5</v>
       </c>
@@ -12620,7 +13034,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="297" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:13">
       <c r="A297" s="1">
         <v>5</v>
       </c>
@@ -12658,7 +13072,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="298" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:13">
       <c r="A298" s="1">
         <v>5</v>
       </c>
@@ -12669,7 +13083,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="299" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:13">
       <c r="A299" s="1">
         <v>5</v>
       </c>
@@ -12707,7 +13121,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="300" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:13">
       <c r="A300" s="1">
         <v>5</v>
       </c>
@@ -12745,7 +13159,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="301" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:13">
       <c r="A301" s="1">
         <v>5</v>
       </c>
@@ -12783,7 +13197,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="302" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:13">
       <c r="A302" s="1">
         <v>5</v>
       </c>
@@ -12821,7 +13235,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="303" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:13">
       <c r="A303" s="1">
         <v>5</v>
       </c>
@@ -12859,7 +13273,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="308" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:13">
       <c r="A308" s="1">
         <v>3</v>
       </c>
@@ -12897,7 +13311,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="309" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:13">
       <c r="A309" s="1">
         <v>3</v>
       </c>
@@ -12935,7 +13349,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="310" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:13">
       <c r="A310" s="1">
         <v>3</v>
       </c>
@@ -12973,7 +13387,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="311" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:13">
       <c r="A311" s="1">
         <v>3</v>
       </c>
@@ -13008,7 +13422,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="312" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:13">
       <c r="A312" s="1">
         <v>3</v>
       </c>
@@ -13016,7 +13430,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="313" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:13">
       <c r="A313" s="1">
         <v>3</v>
       </c>
@@ -13024,7 +13438,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="314" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:13">
       <c r="A314" s="1">
         <v>3</v>
       </c>
@@ -13062,7 +13476,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="315" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:13">
       <c r="A315" s="1">
         <v>3</v>
       </c>
@@ -13070,7 +13484,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="316" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:13">
       <c r="A316" s="1">
         <v>3</v>
       </c>
@@ -13108,7 +13522,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="317" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:13">
       <c r="A317" s="1">
         <v>3</v>
       </c>
@@ -13146,7 +13560,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="318" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:13">
       <c r="A318" s="1">
         <v>3</v>
       </c>
@@ -13184,7 +13598,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="319" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:13">
       <c r="A319" s="1">
         <v>3</v>
       </c>
@@ -13222,7 +13636,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="320" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:13">
       <c r="A320" s="1">
         <v>3</v>
       </c>
@@ -13260,7 +13674,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="321" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:13">
       <c r="A321" s="1">
         <v>3</v>
       </c>
@@ -13298,7 +13712,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="322" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:13">
       <c r="A322" s="1">
         <v>3</v>
       </c>
@@ -13336,7 +13750,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="323" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:13">
       <c r="A323" s="1">
         <v>3</v>
       </c>
@@ -13374,7 +13788,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="324" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:13">
       <c r="A324" s="1">
         <v>3</v>
       </c>
@@ -13382,7 +13796,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="325" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:13">
       <c r="A325" s="1">
         <v>3</v>
       </c>
@@ -13420,7 +13834,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="326" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:13">
       <c r="A326" s="1">
         <v>3</v>
       </c>
@@ -13458,7 +13872,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="327" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:13">
       <c r="A327" s="1">
         <v>3</v>
       </c>
@@ -13496,7 +13910,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="328" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:13">
       <c r="A328" s="1">
         <v>3</v>
       </c>
@@ -13534,7 +13948,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="329" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:13">
       <c r="A329" s="1">
         <v>3</v>
       </c>
@@ -13572,7 +13986,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="330" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:13">
       <c r="A330" s="1">
         <v>3</v>
       </c>
@@ -13610,7 +14024,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="331" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:13">
       <c r="A331" s="1">
         <v>3</v>
       </c>
@@ -13648,7 +14062,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="332" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:13">
       <c r="A332" s="1">
         <v>3</v>
       </c>
@@ -13686,7 +14100,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="333" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:13">
       <c r="A333" s="1">
         <v>3</v>
       </c>
@@ -13724,7 +14138,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="334" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:13">
       <c r="A334" s="1">
         <v>3</v>
       </c>
@@ -13732,7 +14146,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="335" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:13">
       <c r="A335" s="1">
         <v>3</v>
       </c>
@@ -13770,7 +14184,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="336" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:13">
       <c r="A336" s="1">
         <v>3</v>
       </c>
@@ -13808,7 +14222,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="337" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:13">
       <c r="A337" s="1">
         <v>3</v>
       </c>
@@ -13846,7 +14260,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="338" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:13">
       <c r="A338" s="1">
         <v>3</v>
       </c>
@@ -13884,7 +14298,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="339" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:13">
       <c r="A339" s="1">
         <v>3</v>
       </c>
@@ -13922,7 +14336,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="340" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:13">
       <c r="A340" s="1">
         <v>3</v>
       </c>
@@ -13960,7 +14374,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="341" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:13">
       <c r="A341" s="1">
         <v>3</v>
       </c>
@@ -13998,7 +14412,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="342" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:13">
       <c r="A342" s="1">
         <v>3</v>
       </c>
@@ -14036,7 +14450,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="343" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:13">
       <c r="A343" s="1">
         <v>3</v>
       </c>
@@ -14074,7 +14488,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="344" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:13">
       <c r="A344" s="1">
         <v>3</v>
       </c>
@@ -14112,7 +14526,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="345" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:13">
       <c r="A345" s="1">
         <v>3</v>
       </c>
@@ -14120,7 +14534,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="346" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:13">
       <c r="A346" s="1">
         <v>3</v>
       </c>
@@ -14158,7 +14572,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="347" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:13">
       <c r="A347" s="1">
         <v>3</v>
       </c>
@@ -14196,7 +14610,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="348" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:13">
       <c r="A348" s="1">
         <v>3</v>
       </c>
@@ -14234,7 +14648,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="349" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:13">
       <c r="A349" s="1">
         <v>3</v>
       </c>
@@ -14272,7 +14686,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="350" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:13">
       <c r="A350" s="1">
         <v>3</v>
       </c>
@@ -14310,7 +14724,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="351" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:13">
       <c r="A351" s="1">
         <v>3</v>
       </c>
@@ -14348,7 +14762,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="352" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:13">
       <c r="A352" s="1">
         <v>3</v>
       </c>
@@ -14386,7 +14800,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="353" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:14">
       <c r="A353" s="1">
         <v>3</v>
       </c>
@@ -14424,12 +14838,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="354" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:14">
       <c r="B354" s="1" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="357" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:14">
       <c r="A357" s="1">
         <v>4</v>
       </c>
@@ -14467,7 +14881,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="358" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:14">
       <c r="A358" s="1">
         <v>4</v>
       </c>
@@ -14505,7 +14919,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="359" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:14">
       <c r="A359" s="1">
         <v>4</v>
       </c>
@@ -14543,7 +14957,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="360" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:14">
       <c r="A360" s="1">
         <v>4</v>
       </c>
@@ -14581,7 +14995,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="361" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:14">
       <c r="A361" s="1">
         <v>4</v>
       </c>
@@ -14619,7 +15033,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="362" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:14">
       <c r="A362" s="1">
         <v>4</v>
       </c>
@@ -14657,7 +15071,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="363" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:14">
       <c r="A363" s="1">
         <v>4</v>
       </c>
@@ -14695,7 +15109,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="364" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:14">
       <c r="A364" s="1">
         <v>4</v>
       </c>
@@ -14736,7 +15150,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="365" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:14">
       <c r="A365" s="1">
         <v>4</v>
       </c>
@@ -14774,7 +15188,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="366" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:14">
       <c r="A366" s="1">
         <v>4</v>
       </c>
@@ -14812,7 +15226,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="367" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:14">
       <c r="A367" s="1">
         <v>4</v>
       </c>
@@ -14850,7 +15264,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="368" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:14">
       <c r="A368" s="1" t="s">
         <v>272</v>
       </c>
@@ -14858,7 +15272,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="369" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:13">
       <c r="A369" s="1" t="s">
         <v>272</v>
       </c>
@@ -14866,7 +15280,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="370" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:13">
       <c r="A370" s="1" t="s">
         <v>272</v>
       </c>
@@ -14874,7 +15288,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="371" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:13">
       <c r="A371" s="1" t="s">
         <v>272</v>
       </c>
@@ -14882,17 +15296,17 @@
         <v>272</v>
       </c>
     </row>
-    <row r="372" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:13">
       <c r="A372" s="1" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="373" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:13">
       <c r="A373" s="1" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="374" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:13">
       <c r="A374" s="1">
         <v>2</v>
       </c>
@@ -14933,7 +15347,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="375" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:13">
       <c r="A375" s="1">
         <v>2</v>
       </c>
@@ -14974,7 +15388,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="376" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:13">
       <c r="A376" s="1">
         <v>2</v>
       </c>
@@ -15015,7 +15429,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="377" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:13">
       <c r="A377" s="1">
         <v>2</v>
       </c>
@@ -15056,7 +15470,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="378" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:13">
       <c r="A378" s="1">
         <v>2</v>
       </c>
@@ -15097,7 +15511,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="379" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:13">
       <c r="A379" s="1">
         <v>2</v>
       </c>
@@ -15105,7 +15519,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="380" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:13">
       <c r="A380" s="1">
         <v>2</v>
       </c>
@@ -15146,7 +15560,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="381" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:13">
       <c r="A381" s="1">
         <v>2</v>
       </c>
@@ -15187,7 +15601,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="382" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:13">
       <c r="A382" s="1">
         <v>2</v>
       </c>
@@ -15228,7 +15642,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="383" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:13">
       <c r="A383" s="1">
         <v>2</v>
       </c>
@@ -15269,7 +15683,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="384" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:13">
       <c r="A384" s="1">
         <v>2</v>
       </c>
@@ -15310,7 +15724,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="385" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:13">
       <c r="A385" s="1">
         <v>2</v>
       </c>
@@ -15351,7 +15765,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="386" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:13">
       <c r="A386" s="1">
         <v>2</v>
       </c>
@@ -15392,7 +15806,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="387" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:13">
       <c r="A387" s="1">
         <v>2</v>
       </c>
@@ -15433,7 +15847,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="388" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:13">
       <c r="A388" s="1">
         <v>2</v>
       </c>
@@ -15471,7 +15885,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="389" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:13">
       <c r="A389" s="1">
         <v>2</v>
       </c>
@@ -15512,7 +15926,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="390" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:13">
       <c r="A390" s="1">
         <v>2</v>
       </c>
@@ -15553,7 +15967,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="391" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:13">
       <c r="A391" s="1">
         <v>2</v>
       </c>
@@ -15594,7 +16008,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="392" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:13">
       <c r="A392" s="1">
         <v>2</v>
       </c>
@@ -15635,7 +16049,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="393" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:13">
       <c r="A393" s="1">
         <v>2</v>
       </c>
@@ -15676,7 +16090,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="394" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:13">
       <c r="A394" s="1">
         <v>2</v>
       </c>
@@ -15717,7 +16131,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="395" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:13">
       <c r="A395" s="1">
         <v>2</v>
       </c>
@@ -15758,7 +16172,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="396" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:13">
       <c r="A396" s="1">
         <v>2</v>
       </c>
@@ -15799,7 +16213,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="397" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:13">
       <c r="A397" s="1">
         <v>2</v>
       </c>
@@ -15840,7 +16254,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="398" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:13">
       <c r="A398" s="1">
         <v>2</v>
       </c>
@@ -15881,7 +16295,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="399" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:13">
       <c r="A399" s="1">
         <v>2</v>
       </c>
@@ -15922,7 +16336,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="400" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:13">
       <c r="A400" s="1">
         <v>2</v>
       </c>
@@ -15963,7 +16377,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="401" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:13">
       <c r="A401" s="1">
         <v>2</v>
       </c>
@@ -16004,7 +16418,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="402" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:13">
       <c r="A402" s="1">
         <v>2</v>
       </c>
@@ -16042,7 +16456,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="403" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:13">
       <c r="A403" s="1">
         <v>2</v>
       </c>
@@ -16083,7 +16497,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="404" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:13">
       <c r="A404" s="1">
         <v>2</v>
       </c>
@@ -16124,7 +16538,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="405" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:13">
       <c r="A405" s="1">
         <v>2</v>
       </c>
@@ -16165,7 +16579,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="406" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:13">
       <c r="A406" s="1">
         <v>2</v>
       </c>
@@ -16206,7 +16620,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="407" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:13">
       <c r="A407" s="1">
         <v>2</v>
       </c>
@@ -16247,7 +16661,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="408" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:13">
       <c r="A408" s="1">
         <v>2</v>
       </c>
@@ -16288,7 +16702,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="409" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:13">
       <c r="A409" s="1">
         <v>2</v>
       </c>
@@ -16296,7 +16710,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="410" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:13">
       <c r="A410" s="1">
         <v>2</v>
       </c>
@@ -16337,7 +16751,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="411" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:13">
       <c r="A411" s="1">
         <v>2</v>
       </c>
@@ -16378,7 +16792,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="412" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:13">
       <c r="A412" s="1">
         <v>2</v>
       </c>
@@ -16419,7 +16833,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="413" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:13">
       <c r="A413" s="1">
         <v>2</v>
       </c>
@@ -16460,7 +16874,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="414" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:13">
       <c r="A414" s="1" t="s">
         <v>272</v>
       </c>
@@ -16468,7 +16882,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="415" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:13">
       <c r="A415" s="1" t="s">
         <v>272</v>
       </c>
@@ -16476,702 +16890,3426 @@
         <v>272</v>
       </c>
     </row>
-    <row r="417" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A417" s="1">
+    <row r="417" spans="1:13">
+      <c r="A417" s="3">
         <v>1</v>
       </c>
-      <c r="B417" s="1">
+      <c r="B417" s="3">
         <v>1</v>
       </c>
-      <c r="L417" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="418" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A418" s="1">
+      <c r="C417" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="D417" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="E417" s="3">
+        <v>87</v>
+      </c>
+      <c r="F417" s="3">
+        <v>73</v>
+      </c>
+      <c r="G417" s="3">
+        <v>63</v>
+      </c>
+      <c r="H417" s="3">
+        <v>87</v>
+      </c>
+      <c r="I417" s="3">
+        <v>88</v>
+      </c>
+      <c r="J417" s="3">
+        <v>79</v>
+      </c>
+      <c r="K417" s="3">
+        <v>72</v>
+      </c>
+      <c r="L417" s="3">
+        <v>44</v>
+      </c>
+      <c r="M417" s="3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="418" spans="1:13">
+      <c r="A418" s="3">
         <v>1</v>
       </c>
-      <c r="B418" s="1">
+      <c r="B418" s="3">
         <v>2</v>
       </c>
-      <c r="L418" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="419" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A419" s="1">
+      <c r="C418" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="D418" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="E418" s="3">
+        <v>84</v>
+      </c>
+      <c r="F418" s="3">
+        <v>66</v>
+      </c>
+      <c r="G418" s="3">
+        <v>53</v>
+      </c>
+      <c r="H418" s="3">
+        <v>75</v>
+      </c>
+      <c r="I418" s="3">
+        <v>86</v>
+      </c>
+      <c r="J418" s="3">
+        <v>83</v>
+      </c>
+      <c r="K418" s="3">
+        <v>68</v>
+      </c>
+      <c r="L418" s="3">
+        <v>40</v>
+      </c>
+      <c r="M418" s="3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="419" spans="1:13">
+      <c r="A419" s="3">
         <v>1</v>
       </c>
-      <c r="B419" s="1">
+      <c r="B419" s="3">
         <v>3</v>
       </c>
-      <c r="L419" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="420" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A420" s="1">
+      <c r="C419" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="D419" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="E419" s="3">
+        <v>73</v>
+      </c>
+      <c r="F419" s="3">
+        <v>36</v>
+      </c>
+      <c r="G419" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H419" s="3">
+        <v>42</v>
+      </c>
+      <c r="I419" s="3">
+        <v>65</v>
+      </c>
+      <c r="J419" s="3">
+        <v>63</v>
+      </c>
+      <c r="K419" s="3">
+        <v>30</v>
+      </c>
+      <c r="L419" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M419" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="420" spans="1:13">
+      <c r="A420" s="3">
         <v>1</v>
       </c>
-      <c r="B420" s="1">
+      <c r="B420" s="3">
         <v>4</v>
       </c>
-      <c r="L420" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="421" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A421" s="1">
+      <c r="C420" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D420" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="E420" s="3">
+        <v>52</v>
+      </c>
+      <c r="F420" s="3">
+        <v>32</v>
+      </c>
+      <c r="G420" s="3">
+        <v>23</v>
+      </c>
+      <c r="H420" s="3">
+        <v>37</v>
+      </c>
+      <c r="I420" s="3">
+        <v>50</v>
+      </c>
+      <c r="J420" s="3">
+        <v>63</v>
+      </c>
+      <c r="K420" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L420" s="3">
+        <v>27</v>
+      </c>
+      <c r="M420" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="421" spans="1:13">
+      <c r="A421" s="3">
         <v>1</v>
       </c>
-      <c r="B421" s="1">
+      <c r="B421" s="3">
         <v>5</v>
       </c>
-      <c r="L421" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="422" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A422" s="1">
+      <c r="C421" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="D421" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="E421" s="3">
+        <v>70</v>
+      </c>
+      <c r="F421" s="3">
+        <v>60</v>
+      </c>
+      <c r="G421" s="3">
+        <v>46</v>
+      </c>
+      <c r="H421" s="3">
+        <v>92</v>
+      </c>
+      <c r="I421" s="3">
+        <v>85</v>
+      </c>
+      <c r="J421" s="3">
+        <v>77</v>
+      </c>
+      <c r="K421" s="3">
+        <v>79</v>
+      </c>
+      <c r="L421" s="3">
+        <v>65</v>
+      </c>
+      <c r="M421" s="3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="422" spans="1:13">
+      <c r="A422" s="3">
         <v>1</v>
       </c>
-      <c r="B422" s="1">
+      <c r="B422" s="3">
         <v>6</v>
       </c>
-      <c r="L422" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="423" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A423" s="1">
+      <c r="C422" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="D422" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="E422" s="3">
+        <v>80</v>
+      </c>
+      <c r="F422" s="3">
+        <v>40</v>
+      </c>
+      <c r="G422" s="3">
+        <v>56</v>
+      </c>
+      <c r="H422" s="3">
+        <v>60</v>
+      </c>
+      <c r="I422" s="3">
+        <v>74</v>
+      </c>
+      <c r="J422" s="3">
+        <v>51</v>
+      </c>
+      <c r="K422" s="3">
+        <v>45</v>
+      </c>
+      <c r="L422" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M422" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="423" spans="1:13">
+      <c r="A423" s="3">
         <v>1</v>
       </c>
-      <c r="B423" s="1">
+      <c r="B423" s="3">
         <v>7</v>
       </c>
-      <c r="L423" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="424" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A424" s="1">
+      <c r="C423" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="D423" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="E423" s="3">
+        <v>89</v>
+      </c>
+      <c r="F423" s="3">
+        <v>90</v>
+      </c>
+      <c r="G423" s="3">
+        <v>58</v>
+      </c>
+      <c r="H423" s="3">
+        <v>92</v>
+      </c>
+      <c r="I423" s="3">
+        <v>88</v>
+      </c>
+      <c r="J423" s="3">
+        <v>79</v>
+      </c>
+      <c r="K423" s="3">
+        <v>65</v>
+      </c>
+      <c r="L423" s="3">
+        <v>37</v>
+      </c>
+      <c r="M423" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="424" spans="1:13">
+      <c r="A424" s="3">
         <v>1</v>
       </c>
-      <c r="B424" s="1">
+      <c r="B424" s="3">
         <v>8</v>
       </c>
-      <c r="L424" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="425" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A425" s="1">
+      <c r="C424" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="D424" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="E424" s="3">
+        <v>80</v>
+      </c>
+      <c r="F424" s="3">
+        <v>56</v>
+      </c>
+      <c r="G424" s="3">
+        <v>33</v>
+      </c>
+      <c r="H424" s="3">
+        <v>82</v>
+      </c>
+      <c r="I424" s="3">
+        <v>88</v>
+      </c>
+      <c r="J424" s="3">
+        <v>80</v>
+      </c>
+      <c r="K424" s="3">
+        <v>40</v>
+      </c>
+      <c r="L424" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M424" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="425" spans="1:13">
+      <c r="A425" s="3">
         <v>1</v>
       </c>
-      <c r="B425" s="1">
+      <c r="B425" s="3">
         <v>9</v>
       </c>
-      <c r="L425" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="426" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A426" s="1">
+      <c r="C425" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="D425" s="3"/>
+      <c r="E425" s="3">
+        <v>14</v>
+      </c>
+      <c r="F425" s="3">
+        <v>43</v>
+      </c>
+      <c r="G425" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H425" s="3">
+        <v>35</v>
+      </c>
+      <c r="I425" s="3">
+        <v>55</v>
+      </c>
+      <c r="J425" s="3">
+        <v>53</v>
+      </c>
+      <c r="K425" s="3">
+        <v>10</v>
+      </c>
+      <c r="L425" s="3">
+        <v>42</v>
+      </c>
+      <c r="M425" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="426" spans="1:13">
+      <c r="A426" s="3">
         <v>1</v>
       </c>
-      <c r="B426" s="1">
+      <c r="B426" s="3">
         <v>10</v>
       </c>
-      <c r="L426" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="427" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A427" s="1">
+      <c r="C426" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D426" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="E426" s="3">
+        <v>30</v>
+      </c>
+      <c r="F426" s="3">
+        <v>22</v>
+      </c>
+      <c r="G426" s="3">
+        <v>38</v>
+      </c>
+      <c r="H426" s="3">
+        <v>34</v>
+      </c>
+      <c r="I426" s="3">
+        <v>32</v>
+      </c>
+      <c r="J426" s="3">
+        <v>73</v>
+      </c>
+      <c r="K426" s="3">
+        <v>40</v>
+      </c>
+      <c r="L426" s="3">
+        <v>18</v>
+      </c>
+      <c r="M426" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="427" spans="1:13">
+      <c r="A427" s="3">
         <v>1</v>
       </c>
-      <c r="B427" s="1">
+      <c r="B427" s="3">
         <v>11</v>
       </c>
-      <c r="L427" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="428" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A428" s="1">
+      <c r="C427" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="D427" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="E427" s="3">
+        <v>88</v>
+      </c>
+      <c r="F427" s="3">
+        <v>56</v>
+      </c>
+      <c r="G427" s="3">
+        <v>49</v>
+      </c>
+      <c r="H427" s="3">
+        <v>88</v>
+      </c>
+      <c r="I427" s="3">
+        <v>68</v>
+      </c>
+      <c r="J427" s="3">
+        <v>82</v>
+      </c>
+      <c r="K427" s="3">
+        <v>40</v>
+      </c>
+      <c r="L427" s="3">
+        <v>31</v>
+      </c>
+      <c r="M427" s="3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="428" spans="1:13">
+      <c r="A428" s="3">
         <v>1</v>
       </c>
-      <c r="B428" s="1">
+      <c r="B428" s="3">
         <v>12</v>
       </c>
-      <c r="L428" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="429" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A429" s="1">
+      <c r="C428" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="D428" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="E428" s="3">
+        <v>44</v>
+      </c>
+      <c r="F428" s="3">
+        <v>44</v>
+      </c>
+      <c r="G428" s="3">
+        <v>28</v>
+      </c>
+      <c r="H428" s="3">
+        <v>22</v>
+      </c>
+      <c r="I428" s="3">
+        <v>42</v>
+      </c>
+      <c r="J428" s="3">
+        <v>58</v>
+      </c>
+      <c r="K428" s="3">
+        <v>30</v>
+      </c>
+      <c r="L428" s="3">
+        <v>20</v>
+      </c>
+      <c r="M428" s="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="429" spans="1:13">
+      <c r="A429" s="3">
         <v>1</v>
       </c>
-      <c r="B429" s="1">
+      <c r="B429" s="3">
         <v>13</v>
       </c>
-      <c r="L429" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="430" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A430" s="1">
+      <c r="C429" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="D429" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="E429" s="3">
+        <v>83</v>
+      </c>
+      <c r="F429" s="3">
+        <v>59</v>
+      </c>
+      <c r="G429" s="3">
+        <v>43</v>
+      </c>
+      <c r="H429" s="3">
+        <v>73</v>
+      </c>
+      <c r="I429" s="3">
+        <v>88</v>
+      </c>
+      <c r="J429" s="3">
+        <v>75</v>
+      </c>
+      <c r="K429" s="3">
+        <v>65</v>
+      </c>
+      <c r="L429" s="3">
+        <v>33</v>
+      </c>
+      <c r="M429" s="3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="430" spans="1:13">
+      <c r="A430" s="3">
         <v>1</v>
       </c>
-      <c r="B430" s="1">
+      <c r="B430" s="3">
         <v>14</v>
       </c>
-      <c r="L430" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="431" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A431" s="1">
+      <c r="C430" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="D430" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="E430" s="3">
+        <v>62</v>
+      </c>
+      <c r="F430" s="3">
+        <v>46</v>
+      </c>
+      <c r="G430" s="3">
+        <v>33</v>
+      </c>
+      <c r="H430" s="3">
+        <v>48</v>
+      </c>
+      <c r="I430" s="3">
+        <v>89</v>
+      </c>
+      <c r="J430" s="3">
+        <v>83</v>
+      </c>
+      <c r="K430" s="3">
+        <v>60</v>
+      </c>
+      <c r="L430" s="3">
+        <v>31</v>
+      </c>
+      <c r="M430" s="3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="431" spans="1:13">
+      <c r="A431" s="3">
         <v>1</v>
       </c>
-      <c r="B431" s="1">
-        <v>15</v>
-      </c>
-      <c r="L431" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="432" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A432" s="1">
+      <c r="B431" s="3">
+        <v>15</v>
+      </c>
+      <c r="C431" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="D431" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="E431" s="3">
+        <v>80</v>
+      </c>
+      <c r="F431" s="3">
+        <v>58</v>
+      </c>
+      <c r="G431" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H431" s="3">
+        <v>67</v>
+      </c>
+      <c r="I431" s="3">
+        <v>83</v>
+      </c>
+      <c r="J431" s="3">
+        <v>72</v>
+      </c>
+      <c r="K431" s="3">
+        <v>72</v>
+      </c>
+      <c r="L431" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M431" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="432" spans="1:13">
+      <c r="A432" s="3">
         <v>1</v>
       </c>
-      <c r="B432" s="1">
-        <v>16</v>
-      </c>
-      <c r="L432" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="433" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A433" s="1">
+      <c r="B432" s="3">
+        <v>16</v>
+      </c>
+      <c r="C432" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D432" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="E432" s="3">
+        <v>78</v>
+      </c>
+      <c r="F432" s="3">
+        <v>30</v>
+      </c>
+      <c r="G432" s="3">
+        <v>44</v>
+      </c>
+      <c r="H432" s="3">
+        <v>22</v>
+      </c>
+      <c r="I432" s="3">
+        <v>44</v>
+      </c>
+      <c r="J432" s="3">
+        <v>45</v>
+      </c>
+      <c r="K432" s="3">
+        <v>53</v>
+      </c>
+      <c r="L432" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M432" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="433" spans="1:13">
+      <c r="A433" s="3">
         <v>1</v>
       </c>
-      <c r="B433" s="1">
+      <c r="B433" s="3">
         <v>17</v>
       </c>
-      <c r="L433" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="434" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A434" s="1">
+      <c r="C433" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="D433" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="E433" s="3">
+        <v>85</v>
+      </c>
+      <c r="F433" s="3">
+        <v>58</v>
+      </c>
+      <c r="G433" s="3">
+        <v>46</v>
+      </c>
+      <c r="H433" s="3">
+        <v>83</v>
+      </c>
+      <c r="I433" s="3">
+        <v>69</v>
+      </c>
+      <c r="J433" s="3">
+        <v>76</v>
+      </c>
+      <c r="K433" s="3">
+        <v>60</v>
+      </c>
+      <c r="L433" s="3">
+        <v>34</v>
+      </c>
+      <c r="M433" s="3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="434" spans="1:13">
+      <c r="A434" s="3">
         <v>1</v>
       </c>
-      <c r="B434" s="1">
+      <c r="B434" s="3">
         <v>18</v>
       </c>
-      <c r="L434" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="435" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A435" s="1">
+      <c r="C434" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="D434" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="E434" s="3">
+        <v>60</v>
+      </c>
+      <c r="F434" s="3">
+        <v>43</v>
+      </c>
+      <c r="G434" s="3">
+        <v>41</v>
+      </c>
+      <c r="H434" s="3">
+        <v>24</v>
+      </c>
+      <c r="I434" s="3">
+        <v>78</v>
+      </c>
+      <c r="J434" s="3">
+        <v>63</v>
+      </c>
+      <c r="K434" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L434" s="3">
+        <v>35</v>
+      </c>
+      <c r="M434" s="3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="435" spans="1:13">
+      <c r="A435" s="3">
         <v>1</v>
       </c>
-      <c r="B435" s="1">
+      <c r="B435" s="3">
         <v>19</v>
       </c>
-      <c r="L435" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="436" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A436" s="1">
+      <c r="C435" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="D435" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="E435" s="3"/>
+      <c r="F435" s="3"/>
+      <c r="G435" s="3"/>
+      <c r="H435" s="3"/>
+      <c r="I435" s="3"/>
+      <c r="J435" s="3"/>
+      <c r="K435" s="3"/>
+      <c r="L435" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="M435" s="3"/>
+    </row>
+    <row r="436" spans="1:13">
+      <c r="A436" s="3">
         <v>1</v>
       </c>
-      <c r="B436" s="1">
+      <c r="B436" s="3">
         <v>20</v>
       </c>
-      <c r="L436" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="437" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A437" s="1">
+      <c r="C436" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="D436" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="E436" s="3"/>
+      <c r="F436" s="3"/>
+      <c r="G436" s="3"/>
+      <c r="H436" s="3"/>
+      <c r="I436" s="3"/>
+      <c r="J436" s="3"/>
+      <c r="K436" s="3"/>
+      <c r="L436" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="M436" s="3"/>
+    </row>
+    <row r="437" spans="1:13">
+      <c r="A437" s="3">
         <v>1</v>
       </c>
-      <c r="B437" s="1">
+      <c r="B437" s="3">
         <v>21</v>
       </c>
-      <c r="L437" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="438" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A438" s="1">
+      <c r="C437" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="D437" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="E437" s="3">
+        <v>75</v>
+      </c>
+      <c r="F437" s="3">
+        <v>42</v>
+      </c>
+      <c r="G437" s="3">
+        <v>37</v>
+      </c>
+      <c r="H437" s="3">
+        <v>26</v>
+      </c>
+      <c r="I437" s="3">
+        <v>33</v>
+      </c>
+      <c r="J437" s="3">
+        <v>31</v>
+      </c>
+      <c r="K437" s="3">
+        <v>30</v>
+      </c>
+      <c r="L437" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M437" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="438" spans="1:13">
+      <c r="A438" s="3">
         <v>1</v>
       </c>
-      <c r="B438" s="1">
+      <c r="B438" s="3">
         <v>22</v>
       </c>
-      <c r="L438" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="439" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A439" s="1">
+      <c r="C438" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="D438" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="E438" s="3">
+        <v>84</v>
+      </c>
+      <c r="F438" s="3">
+        <v>58</v>
+      </c>
+      <c r="G438" s="3">
+        <v>66</v>
+      </c>
+      <c r="H438" s="3">
+        <v>83</v>
+      </c>
+      <c r="I438" s="3">
+        <v>80</v>
+      </c>
+      <c r="J438" s="3">
+        <v>80</v>
+      </c>
+      <c r="K438" s="3">
+        <v>58</v>
+      </c>
+      <c r="L438" s="3">
+        <v>37</v>
+      </c>
+      <c r="M438" s="3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="439" spans="1:13">
+      <c r="A439" s="3">
         <v>1</v>
       </c>
-      <c r="B439" s="1">
+      <c r="B439" s="3">
         <v>23</v>
       </c>
-      <c r="L439" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="440" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A440" s="1">
+      <c r="C439" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="D439" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="E439" s="3">
+        <v>87</v>
+      </c>
+      <c r="F439" s="3">
+        <v>49</v>
+      </c>
+      <c r="G439" s="3">
+        <v>33</v>
+      </c>
+      <c r="H439" s="3">
+        <v>73</v>
+      </c>
+      <c r="I439" s="3">
+        <v>80</v>
+      </c>
+      <c r="J439" s="3">
+        <v>67</v>
+      </c>
+      <c r="K439" s="3">
+        <v>65</v>
+      </c>
+      <c r="L439" s="3">
+        <v>40</v>
+      </c>
+      <c r="M439" s="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="440" spans="1:13">
+      <c r="A440" s="3">
         <v>1</v>
       </c>
-      <c r="B440" s="1">
+      <c r="B440" s="3">
         <v>24</v>
       </c>
-      <c r="L440" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="441" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A441" s="1">
+      <c r="C440" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="D440" s="3"/>
+      <c r="E440" s="3">
+        <v>30</v>
+      </c>
+      <c r="F440" s="3">
+        <v>33</v>
+      </c>
+      <c r="G440" s="3">
+        <v>33</v>
+      </c>
+      <c r="H440" s="3">
+        <v>21</v>
+      </c>
+      <c r="I440" s="3">
+        <v>42</v>
+      </c>
+      <c r="J440" s="3">
+        <v>35</v>
+      </c>
+      <c r="K440" s="3">
+        <v>26</v>
+      </c>
+      <c r="L440" s="3">
+        <v>25</v>
+      </c>
+      <c r="M440" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="441" spans="1:13">
+      <c r="A441" s="3">
         <v>1</v>
       </c>
-      <c r="B441" s="1">
+      <c r="B441" s="3">
         <v>25</v>
       </c>
-      <c r="L441" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="442" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A442" s="1">
+      <c r="C441" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="D441" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="E441" s="3">
+        <v>87</v>
+      </c>
+      <c r="F441" s="3">
+        <v>48</v>
+      </c>
+      <c r="G441" s="3">
+        <v>37</v>
+      </c>
+      <c r="H441" s="3">
+        <v>83</v>
+      </c>
+      <c r="I441" s="3">
+        <v>83</v>
+      </c>
+      <c r="J441" s="3">
+        <v>75</v>
+      </c>
+      <c r="K441" s="3">
+        <v>55</v>
+      </c>
+      <c r="L441" s="3">
+        <v>36</v>
+      </c>
+      <c r="M441" s="3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="442" spans="1:13">
+      <c r="A442" s="3">
         <v>1</v>
       </c>
-      <c r="B442" s="1">
+      <c r="B442" s="3">
         <v>26</v>
       </c>
-      <c r="L442" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="443" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A443" s="1">
+      <c r="C442" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="D442" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="E442" s="3">
+        <v>88</v>
+      </c>
+      <c r="F442" s="3">
+        <v>60</v>
+      </c>
+      <c r="G442" s="3">
+        <v>46</v>
+      </c>
+      <c r="H442" s="3">
+        <v>93</v>
+      </c>
+      <c r="I442" s="3">
+        <v>85</v>
+      </c>
+      <c r="J442" s="3">
+        <v>72</v>
+      </c>
+      <c r="K442" s="3">
+        <v>70</v>
+      </c>
+      <c r="L442" s="3">
+        <v>47</v>
+      </c>
+      <c r="M442" s="3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="443" spans="1:13">
+      <c r="A443" s="3">
         <v>1</v>
       </c>
-      <c r="B443" s="1">
+      <c r="B443" s="3">
         <v>27</v>
       </c>
-      <c r="L443" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="444" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A444" s="1">
+      <c r="C443" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="D443" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="E443" s="3">
+        <v>74</v>
+      </c>
+      <c r="F443" s="3">
+        <v>40</v>
+      </c>
+      <c r="G443" s="3">
+        <v>30</v>
+      </c>
+      <c r="H443" s="3">
+        <v>71</v>
+      </c>
+      <c r="I443" s="3">
+        <v>58</v>
+      </c>
+      <c r="J443" s="3">
+        <v>57</v>
+      </c>
+      <c r="K443" s="3">
+        <v>45</v>
+      </c>
+      <c r="L443" s="3">
+        <v>36</v>
+      </c>
+      <c r="M443" s="3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="444" spans="1:13">
+      <c r="A444" s="3">
         <v>1</v>
       </c>
-      <c r="B444" s="1">
+      <c r="B444" s="3">
         <v>28</v>
       </c>
-      <c r="L444" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="445" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A445" s="1">
+      <c r="C444" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D444" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="E444" s="3">
+        <v>40</v>
+      </c>
+      <c r="F444" s="3">
+        <v>38</v>
+      </c>
+      <c r="G444" s="3">
+        <v>68</v>
+      </c>
+      <c r="H444" s="3">
+        <v>65</v>
+      </c>
+      <c r="I444" s="3">
+        <v>52</v>
+      </c>
+      <c r="J444" s="3">
+        <v>69</v>
+      </c>
+      <c r="K444" s="3">
+        <v>34</v>
+      </c>
+      <c r="L444" s="3">
+        <v>26</v>
+      </c>
+      <c r="M444" s="3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="445" spans="1:13">
+      <c r="A445" s="3">
         <v>1</v>
       </c>
-      <c r="B445" s="1">
+      <c r="B445" s="3">
         <v>29</v>
       </c>
-      <c r="L445" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="446" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A446" s="1">
+      <c r="C445" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="D445" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="E445" s="3">
+        <v>61</v>
+      </c>
+      <c r="F445" s="3">
+        <v>46</v>
+      </c>
+      <c r="G445" s="3">
+        <v>41</v>
+      </c>
+      <c r="H445" s="3">
+        <v>46</v>
+      </c>
+      <c r="I445" s="3">
+        <v>48</v>
+      </c>
+      <c r="J445" s="3">
+        <v>54</v>
+      </c>
+      <c r="K445" s="3">
+        <v>30</v>
+      </c>
+      <c r="L445" s="3">
+        <v>22</v>
+      </c>
+      <c r="M445" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="446" spans="1:13">
+      <c r="A446" s="3">
         <v>1</v>
       </c>
-      <c r="B446" s="1">
+      <c r="B446" s="3">
         <v>30</v>
       </c>
-      <c r="L446" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="447" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A447" s="1">
+      <c r="C446" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="D446" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="E446" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F446" s="3">
+        <v>82</v>
+      </c>
+      <c r="G446" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H446" s="3">
+        <v>63</v>
+      </c>
+      <c r="I446" s="3">
+        <v>68</v>
+      </c>
+      <c r="J446" s="3">
+        <v>60</v>
+      </c>
+      <c r="K446" s="3">
+        <v>42</v>
+      </c>
+      <c r="L446" s="3">
+        <v>31</v>
+      </c>
+      <c r="M446" s="3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="447" spans="1:13">
+      <c r="A447" s="3">
         <v>1</v>
       </c>
-      <c r="B447" s="1">
+      <c r="B447" s="3">
         <v>31</v>
       </c>
-      <c r="L447" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="448" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A448" s="1">
+      <c r="C447" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="D447" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="E447" s="3">
+        <v>87</v>
+      </c>
+      <c r="F447" s="3">
+        <v>28</v>
+      </c>
+      <c r="G447" s="3">
+        <v>28</v>
+      </c>
+      <c r="H447" s="3">
+        <v>61</v>
+      </c>
+      <c r="I447" s="3">
+        <v>77</v>
+      </c>
+      <c r="J447" s="3">
+        <v>20</v>
+      </c>
+      <c r="K447" s="3">
+        <v>63</v>
+      </c>
+      <c r="L447" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M447" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="448" spans="1:13">
+      <c r="A448" s="3">
         <v>1</v>
       </c>
-      <c r="B448" s="1">
+      <c r="B448" s="3">
         <v>32</v>
       </c>
-      <c r="L448" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="449" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A449" s="1">
+      <c r="C448" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="D448" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="E448" s="3">
+        <v>89</v>
+      </c>
+      <c r="F448" s="3">
+        <v>59</v>
+      </c>
+      <c r="G448" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H448" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I448" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J448" s="3">
+        <v>78</v>
+      </c>
+      <c r="K448" s="3">
+        <v>38</v>
+      </c>
+      <c r="L448" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M448" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="449" spans="1:13">
+      <c r="A449" s="3">
         <v>1</v>
       </c>
-      <c r="B449" s="1">
+      <c r="B449" s="3">
         <v>33</v>
       </c>
-      <c r="L449" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="450" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A450" s="1">
+      <c r="C449" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="D449" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="E449" s="3">
+        <v>84</v>
+      </c>
+      <c r="F449" s="3">
+        <v>73</v>
+      </c>
+      <c r="G449" s="3">
+        <v>51</v>
+      </c>
+      <c r="H449" s="3">
+        <v>52</v>
+      </c>
+      <c r="I449" s="3">
+        <v>50</v>
+      </c>
+      <c r="J449" s="3">
+        <v>63</v>
+      </c>
+      <c r="K449" s="3">
+        <v>68</v>
+      </c>
+      <c r="L449" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M449" s="3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="450" spans="1:13">
+      <c r="A450" s="3">
         <v>1</v>
       </c>
-      <c r="B450" s="1">
+      <c r="B450" s="3">
         <v>34</v>
       </c>
-      <c r="L450" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="451" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A451" s="1">
+      <c r="C450" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="D450" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="E450" s="3">
+        <v>88</v>
+      </c>
+      <c r="F450" s="3">
+        <v>47</v>
+      </c>
+      <c r="G450" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H450" s="3">
+        <v>66</v>
+      </c>
+      <c r="I450" s="3">
+        <v>39</v>
+      </c>
+      <c r="J450" s="3">
+        <v>48</v>
+      </c>
+      <c r="K450" s="3">
+        <v>28</v>
+      </c>
+      <c r="L450" s="3">
+        <v>30</v>
+      </c>
+      <c r="M450" s="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="451" spans="1:13">
+      <c r="A451" s="3">
         <v>1</v>
       </c>
-      <c r="B451" s="1">
+      <c r="B451" s="3">
+        <v>36</v>
+      </c>
+      <c r="C451" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="D451" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="E451" s="3">
+        <v>55</v>
+      </c>
+      <c r="F451" s="3">
+        <v>53</v>
+      </c>
+      <c r="G451" s="3">
+        <v>44</v>
+      </c>
+      <c r="H451" s="3">
+        <v>43</v>
+      </c>
+      <c r="I451" s="3">
+        <v>65</v>
+      </c>
+      <c r="J451" s="3">
+        <v>61</v>
+      </c>
+      <c r="K451" s="3">
+        <v>45</v>
+      </c>
+      <c r="L451" s="3">
+        <v>32</v>
+      </c>
+      <c r="M451" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="452" spans="1:13">
+      <c r="A452" s="3">
+        <v>1</v>
+      </c>
+      <c r="B452" s="3">
+        <v>37</v>
+      </c>
+      <c r="C452" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="D452" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="E452" s="3">
+        <v>87</v>
+      </c>
+      <c r="F452" s="3">
+        <v>65</v>
+      </c>
+      <c r="G452" s="3">
+        <v>48</v>
+      </c>
+      <c r="H452" s="3">
+        <v>55</v>
+      </c>
+      <c r="I452" s="3">
+        <v>79</v>
+      </c>
+      <c r="J452" s="3">
+        <v>63</v>
+      </c>
+      <c r="K452" s="3">
         <v>35</v>
       </c>
-      <c r="L451" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="452" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A452" s="1">
+      <c r="L452" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M452" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="453" spans="1:13">
+      <c r="A453" s="3">
         <v>1</v>
       </c>
-      <c r="B452" s="1">
+      <c r="B453" s="3">
+        <v>38</v>
+      </c>
+      <c r="C453" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="D453" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="E453" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F453" s="3">
+        <v>20</v>
+      </c>
+      <c r="G453" s="3">
+        <v>38</v>
+      </c>
+      <c r="H453" s="3">
+        <v>34</v>
+      </c>
+      <c r="I453" s="3">
+        <v>30</v>
+      </c>
+      <c r="J453" s="3">
+        <v>49</v>
+      </c>
+      <c r="K453" s="3">
+        <v>25</v>
+      </c>
+      <c r="L453" s="3">
+        <v>30</v>
+      </c>
+      <c r="M453" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="454" spans="1:13">
+      <c r="A454" s="3">
+        <v>1</v>
+      </c>
+      <c r="B454" s="3">
+        <v>39</v>
+      </c>
+      <c r="C454" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D454" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="E454" s="3">
+        <v>75</v>
+      </c>
+      <c r="F454" s="3">
+        <v>39</v>
+      </c>
+      <c r="G454" s="3">
+        <v>38</v>
+      </c>
+      <c r="H454" s="3">
+        <v>72</v>
+      </c>
+      <c r="I454" s="3">
+        <v>55</v>
+      </c>
+      <c r="J454" s="3">
+        <v>63</v>
+      </c>
+      <c r="K454" s="3">
+        <v>42</v>
+      </c>
+      <c r="L454" s="3">
+        <v>32</v>
+      </c>
+      <c r="M454" s="3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="455" spans="1:13">
+      <c r="A455" s="3">
+        <v>1</v>
+      </c>
+      <c r="B455" s="3">
+        <v>40</v>
+      </c>
+      <c r="C455" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="D455" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="E455" s="3">
+        <v>88</v>
+      </c>
+      <c r="F455" s="3">
+        <v>70</v>
+      </c>
+      <c r="G455" s="3">
+        <v>68</v>
+      </c>
+      <c r="H455" s="3">
+        <v>87</v>
+      </c>
+      <c r="I455" s="3">
+        <v>88</v>
+      </c>
+      <c r="J455" s="3">
+        <v>72</v>
+      </c>
+      <c r="K455" s="3">
+        <v>67</v>
+      </c>
+      <c r="L455" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M455" s="3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="456" spans="1:13">
+      <c r="A456" s="3">
+        <v>1</v>
+      </c>
+      <c r="B456" s="3">
+        <v>41</v>
+      </c>
+      <c r="C456" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D456" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="E456" s="3">
+        <v>74</v>
+      </c>
+      <c r="F456" s="3">
+        <v>49</v>
+      </c>
+      <c r="G456" s="3">
+        <v>68</v>
+      </c>
+      <c r="H456" s="3">
+        <v>84</v>
+      </c>
+      <c r="I456" s="3">
+        <v>60</v>
+      </c>
+      <c r="J456" s="3">
+        <v>76</v>
+      </c>
+      <c r="K456" s="3">
+        <v>25</v>
+      </c>
+      <c r="L456" s="3">
         <v>36</v>
       </c>
-      <c r="L452" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="453" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A453" s="1">
+      <c r="M456" s="3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="457" spans="1:13">
+      <c r="A457" s="3">
         <v>1</v>
       </c>
-      <c r="B453" s="1">
+      <c r="B457" s="3">
+        <v>42</v>
+      </c>
+      <c r="C457" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="D457" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="E457" s="3">
+        <v>87</v>
+      </c>
+      <c r="F457" s="3">
+        <v>63</v>
+      </c>
+      <c r="G457" s="3">
+        <v>38</v>
+      </c>
+      <c r="H457" s="3">
+        <v>82</v>
+      </c>
+      <c r="I457" s="3">
+        <v>81</v>
+      </c>
+      <c r="J457" s="3">
+        <v>69</v>
+      </c>
+      <c r="K457" s="3">
+        <v>70</v>
+      </c>
+      <c r="L457" s="3">
+        <v>32</v>
+      </c>
+      <c r="M457" s="3">
         <v>37</v>
       </c>
-      <c r="L453" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="454" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A454" s="1">
+    </row>
+    <row r="458" spans="1:13">
+      <c r="A458" s="3">
         <v>1</v>
       </c>
-      <c r="B454" s="1">
-        <v>38</v>
-      </c>
-      <c r="L454" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="455" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A455" s="1">
+      <c r="B458" s="3">
+        <v>43</v>
+      </c>
+      <c r="C458" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="D458" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="E458" s="3">
+        <v>24</v>
+      </c>
+      <c r="F458" s="3">
+        <v>30</v>
+      </c>
+      <c r="G458" s="3">
+        <v>36</v>
+      </c>
+      <c r="H458" s="3">
+        <v>41</v>
+      </c>
+      <c r="I458" s="3">
+        <v>30</v>
+      </c>
+      <c r="J458" s="3">
+        <v>24</v>
+      </c>
+      <c r="K458" s="3">
+        <v>30</v>
+      </c>
+      <c r="L458" s="3">
+        <v>30</v>
+      </c>
+      <c r="M458" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="459" spans="1:13">
+      <c r="A459" s="3">
         <v>1</v>
       </c>
-      <c r="B455" s="1">
+      <c r="B459" s="3">
+        <v>44</v>
+      </c>
+      <c r="C459" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D459" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="E459" s="3">
+        <v>65</v>
+      </c>
+      <c r="F459" s="3">
+        <v>44</v>
+      </c>
+      <c r="G459" s="3">
+        <v>36</v>
+      </c>
+      <c r="H459" s="3">
+        <v>68</v>
+      </c>
+      <c r="I459" s="3">
+        <v>59</v>
+      </c>
+      <c r="J459" s="3">
+        <v>64</v>
+      </c>
+      <c r="K459" s="3">
+        <v>35</v>
+      </c>
+      <c r="L459" s="3">
+        <v>35</v>
+      </c>
+      <c r="M459" s="3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="460" spans="1:13">
+      <c r="A460" s="3">
+        <v>1</v>
+      </c>
+      <c r="B460" s="3">
+        <v>45</v>
+      </c>
+      <c r="C460" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="D460" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="E460" s="3">
+        <v>79</v>
+      </c>
+      <c r="F460" s="3">
+        <v>37</v>
+      </c>
+      <c r="G460" s="3">
+        <v>46</v>
+      </c>
+      <c r="H460" s="3">
+        <v>22</v>
+      </c>
+      <c r="I460" s="3">
+        <v>37</v>
+      </c>
+      <c r="J460" s="3">
+        <v>41</v>
+      </c>
+      <c r="K460" s="3">
+        <v>35</v>
+      </c>
+      <c r="L460" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M460" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="461" spans="1:13">
+      <c r="A461" s="3">
+        <v>1</v>
+      </c>
+      <c r="B461" s="3">
+        <v>47</v>
+      </c>
+      <c r="C461" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="D461" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="E461" s="3"/>
+      <c r="F461" s="3"/>
+      <c r="G461" s="3"/>
+      <c r="H461" s="3"/>
+      <c r="I461" s="3"/>
+      <c r="J461" s="3"/>
+      <c r="K461" s="3"/>
+      <c r="L461" s="3"/>
+      <c r="M461" s="3"/>
+    </row>
+    <row r="462" spans="1:13">
+      <c r="A462" s="3">
+        <v>1</v>
+      </c>
+      <c r="B462" s="3">
+        <v>48</v>
+      </c>
+      <c r="C462" s="3" t="s">
+        <v>619</v>
+      </c>
+      <c r="D462" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="E462" s="3"/>
+      <c r="F462" s="3"/>
+      <c r="G462" s="3"/>
+      <c r="H462" s="3"/>
+      <c r="I462" s="3"/>
+      <c r="J462" s="3"/>
+      <c r="K462" s="3"/>
+      <c r="L462" s="3"/>
+      <c r="M462" s="3"/>
+    </row>
+    <row r="463" spans="1:13">
+      <c r="A463" s="3">
+        <v>1</v>
+      </c>
+      <c r="B463" s="3">
+        <v>49</v>
+      </c>
+      <c r="C463" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="D463" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="E463" s="3"/>
+      <c r="F463" s="3"/>
+      <c r="G463" s="3"/>
+      <c r="H463" s="3"/>
+      <c r="I463" s="3"/>
+      <c r="J463" s="3"/>
+      <c r="K463" s="3"/>
+      <c r="L463" s="3"/>
+      <c r="M463" s="3"/>
+    </row>
+    <row r="464" spans="1:13">
+      <c r="A464" s="3">
+        <v>1</v>
+      </c>
+      <c r="B464" s="3">
+        <v>50</v>
+      </c>
+      <c r="C464" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="D464" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="E464" s="3">
+        <v>25</v>
+      </c>
+      <c r="F464" s="3">
+        <v>30</v>
+      </c>
+      <c r="G464" s="3">
+        <v>15</v>
+      </c>
+      <c r="H464" s="3">
+        <v>37</v>
+      </c>
+      <c r="I464" s="3">
+        <v>40</v>
+      </c>
+      <c r="J464" s="3">
+        <v>47</v>
+      </c>
+      <c r="K464" s="3">
+        <v>32</v>
+      </c>
+      <c r="L464" s="3">
+        <v>9</v>
+      </c>
+      <c r="M464" s="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="465" spans="1:13">
+      <c r="A465" s="3">
+        <v>1</v>
+      </c>
+      <c r="B465" s="3">
+        <v>51</v>
+      </c>
+      <c r="C465" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D465" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="E465" s="3"/>
+      <c r="F465" s="3"/>
+      <c r="G465" s="3"/>
+      <c r="H465" s="3"/>
+      <c r="I465" s="3"/>
+      <c r="J465" s="3"/>
+      <c r="K465" s="3"/>
+      <c r="L465" s="3"/>
+      <c r="M465" s="3"/>
+    </row>
+    <row r="466" spans="1:13">
+      <c r="A466" s="3">
+        <v>1</v>
+      </c>
+      <c r="B466" s="3">
+        <v>52</v>
+      </c>
+      <c r="C466" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="D466" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="E466" s="3">
+        <v>55</v>
+      </c>
+      <c r="F466" s="3">
+        <v>30</v>
+      </c>
+      <c r="G466" s="3">
+        <v>54</v>
+      </c>
+      <c r="H466" s="3">
+        <v>45</v>
+      </c>
+      <c r="I466" s="3">
+        <v>50</v>
+      </c>
+      <c r="J466" s="3">
         <v>39</v>
       </c>
-      <c r="L455" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="456" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A456" s="1">
+      <c r="K466" s="3">
+        <v>36</v>
+      </c>
+      <c r="L466" s="3">
+        <v>21</v>
+      </c>
+      <c r="M466" s="3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="467" spans="1:13">
+      <c r="A467" s="3">
         <v>1</v>
       </c>
-      <c r="B456" s="1">
+      <c r="B467" s="3">
+        <v>53</v>
+      </c>
+      <c r="C467" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="D467" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="E467" s="3">
+        <v>27</v>
+      </c>
+      <c r="F467" s="3">
+        <v>39</v>
+      </c>
+      <c r="G467" s="3">
+        <v>32</v>
+      </c>
+      <c r="H467" s="3">
+        <v>21</v>
+      </c>
+      <c r="I467" s="3">
+        <v>26</v>
+      </c>
+      <c r="J467" s="3">
+        <v>44</v>
+      </c>
+      <c r="K467" s="3">
+        <v>39</v>
+      </c>
+      <c r="L467" s="3">
+        <v>35</v>
+      </c>
+      <c r="M467" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="468" spans="1:13">
+      <c r="A468" s="3">
+        <v>1</v>
+      </c>
+      <c r="B468" s="3">
+        <v>54</v>
+      </c>
+      <c r="C468" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="D468" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="E468" s="3">
+        <v>79</v>
+      </c>
+      <c r="F468" s="3">
+        <v>25</v>
+      </c>
+      <c r="G468" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H468" s="3">
         <v>40</v>
       </c>
-      <c r="L456" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="457" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A457" s="1">
+      <c r="I468" s="3">
+        <v>25</v>
+      </c>
+      <c r="J468" s="3">
+        <v>39</v>
+      </c>
+      <c r="K468" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L468" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M468" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="469" spans="1:13">
+      <c r="A469" s="3">
         <v>1</v>
       </c>
-      <c r="B457" s="1">
+      <c r="B469" s="3">
+        <v>55</v>
+      </c>
+      <c r="C469" s="3" t="s">
+        <v>628</v>
+      </c>
+      <c r="D469" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="E469" s="3">
+        <v>79</v>
+      </c>
+      <c r="F469" s="3">
+        <v>40</v>
+      </c>
+      <c r="G469" s="3">
+        <v>62</v>
+      </c>
+      <c r="H469" s="3">
+        <v>71</v>
+      </c>
+      <c r="I469" s="3">
+        <v>75</v>
+      </c>
+      <c r="J469" s="3">
+        <v>52</v>
+      </c>
+      <c r="K469" s="3">
+        <v>32</v>
+      </c>
+      <c r="L469" s="3">
+        <v>35</v>
+      </c>
+      <c r="M469" s="3">
         <v>41</v>
       </c>
-      <c r="L457" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="458" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A458" s="1">
+    </row>
+    <row r="470" spans="1:13">
+      <c r="A470" s="3">
         <v>1</v>
       </c>
-      <c r="B458" s="1">
+      <c r="B470" s="3">
+        <v>56</v>
+      </c>
+      <c r="C470" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="D470" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="E470" s="3">
+        <v>19</v>
+      </c>
+      <c r="F470" s="3">
+        <v>24</v>
+      </c>
+      <c r="G470" s="3">
+        <v>23</v>
+      </c>
+      <c r="H470" s="3">
+        <v>29</v>
+      </c>
+      <c r="I470" s="3">
+        <v>25</v>
+      </c>
+      <c r="J470" s="3">
+        <v>34</v>
+      </c>
+      <c r="K470" s="3">
+        <v>24</v>
+      </c>
+      <c r="L470" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M470" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="471" spans="1:13">
+      <c r="A471" s="3">
+        <v>1</v>
+      </c>
+      <c r="B471" s="3">
+        <v>57</v>
+      </c>
+      <c r="C471" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="D471" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="E471" s="3">
+        <v>70</v>
+      </c>
+      <c r="F471" s="3">
+        <v>23</v>
+      </c>
+      <c r="G471" s="3">
+        <v>48</v>
+      </c>
+      <c r="H471" s="3">
+        <v>50</v>
+      </c>
+      <c r="I471" s="3">
+        <v>35</v>
+      </c>
+      <c r="J471" s="3">
+        <v>57</v>
+      </c>
+      <c r="K471" s="3">
+        <v>27</v>
+      </c>
+      <c r="L471" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="M471" s="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="472" spans="1:13">
+      <c r="A472" s="3">
+        <v>1</v>
+      </c>
+      <c r="B472" s="3">
+        <v>58</v>
+      </c>
+      <c r="C472" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="D472" s="3" t="s">
+        <v>636</v>
+      </c>
+      <c r="E472" s="3">
+        <v>79</v>
+      </c>
+      <c r="F472" s="3">
+        <v>40</v>
+      </c>
+      <c r="G472" s="3">
+        <v>59</v>
+      </c>
+      <c r="H472" s="3">
+        <v>51</v>
+      </c>
+      <c r="I472" s="3">
+        <v>47</v>
+      </c>
+      <c r="J472" s="3">
+        <v>51</v>
+      </c>
+      <c r="K472" s="3">
+        <v>43</v>
+      </c>
+      <c r="L472" s="3">
+        <v>48</v>
+      </c>
+      <c r="M472" s="3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="473" spans="1:13">
+      <c r="A473" s="3">
+        <v>1</v>
+      </c>
+      <c r="B473" s="3">
+        <v>59</v>
+      </c>
+      <c r="C473" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="D473" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="E473" s="3">
+        <v>76</v>
+      </c>
+      <c r="F473" s="3">
+        <v>45</v>
+      </c>
+      <c r="G473" s="3">
+        <v>40</v>
+      </c>
+      <c r="H473" s="3">
+        <v>50</v>
+      </c>
+      <c r="I473" s="3">
+        <v>25</v>
+      </c>
+      <c r="J473" s="3">
+        <v>48</v>
+      </c>
+      <c r="K473" s="3">
+        <v>31</v>
+      </c>
+      <c r="L473" s="3">
+        <v>17</v>
+      </c>
+      <c r="M473" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="474" spans="1:13">
+      <c r="A474" s="3">
+        <v>1</v>
+      </c>
+      <c r="B474" s="3">
+        <v>60</v>
+      </c>
+      <c r="C474" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="D474" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="E474" s="3"/>
+      <c r="F474" s="3"/>
+      <c r="G474" s="3"/>
+      <c r="H474" s="3"/>
+      <c r="I474" s="3"/>
+      <c r="J474" s="3"/>
+      <c r="K474" s="3"/>
+      <c r="L474" s="3"/>
+      <c r="M474" s="3"/>
+    </row>
+    <row r="475" spans="1:13">
+      <c r="A475" s="3">
+        <v>1</v>
+      </c>
+      <c r="B475" s="3">
+        <v>61</v>
+      </c>
+      <c r="C475" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D475" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="E475" s="3">
+        <v>79</v>
+      </c>
+      <c r="F475" s="3">
+        <v>22</v>
+      </c>
+      <c r="G475" s="3">
+        <v>33</v>
+      </c>
+      <c r="H475" s="3">
+        <v>30</v>
+      </c>
+      <c r="I475" s="3">
+        <v>39</v>
+      </c>
+      <c r="J475" s="3">
+        <v>37</v>
+      </c>
+      <c r="K475" s="3">
+        <v>23</v>
+      </c>
+      <c r="L475" s="3">
+        <v>11</v>
+      </c>
+      <c r="M475" s="3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="476" spans="1:13">
+      <c r="A476" s="3">
+        <v>1</v>
+      </c>
+      <c r="B476" s="3">
+        <v>62</v>
+      </c>
+      <c r="C476" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="D476" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="E476" s="3"/>
+      <c r="F476" s="3"/>
+      <c r="G476" s="3"/>
+      <c r="H476" s="3"/>
+      <c r="I476" s="3"/>
+      <c r="J476" s="3"/>
+      <c r="K476" s="3"/>
+      <c r="L476" s="3"/>
+      <c r="M476" s="3"/>
+    </row>
+    <row r="477" spans="1:13">
+      <c r="A477" s="3">
+        <v>1</v>
+      </c>
+      <c r="B477" s="3">
+        <v>63</v>
+      </c>
+      <c r="C477" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="D477" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="E477" s="3">
+        <v>79</v>
+      </c>
+      <c r="F477" s="3">
+        <v>35</v>
+      </c>
+      <c r="G477" s="3">
+        <v>76</v>
+      </c>
+      <c r="H477" s="3">
+        <v>70</v>
+      </c>
+      <c r="I477" s="3">
+        <v>68</v>
+      </c>
+      <c r="J477" s="3">
+        <v>49</v>
+      </c>
+      <c r="K477" s="3">
+        <v>35</v>
+      </c>
+      <c r="L477" s="3">
+        <v>48</v>
+      </c>
+      <c r="M477" s="3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="478" spans="1:13">
+      <c r="A478" s="3">
+        <v>1</v>
+      </c>
+      <c r="B478" s="3">
+        <v>64</v>
+      </c>
+      <c r="C478" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="D478" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E478" s="3"/>
+      <c r="F478" s="3"/>
+      <c r="G478" s="3"/>
+      <c r="H478" s="3"/>
+      <c r="I478" s="3"/>
+      <c r="J478" s="3"/>
+      <c r="K478" s="3"/>
+      <c r="L478" s="3"/>
+      <c r="M478" s="3"/>
+    </row>
+    <row r="479" spans="1:13">
+      <c r="A479" s="3">
+        <v>1</v>
+      </c>
+      <c r="B479" s="3">
+        <v>65</v>
+      </c>
+      <c r="C479" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="D479" s="3" t="s">
+        <v>647</v>
+      </c>
+      <c r="E479" s="3">
+        <v>25</v>
+      </c>
+      <c r="F479" s="3">
+        <v>27</v>
+      </c>
+      <c r="G479" s="3">
+        <v>15</v>
+      </c>
+      <c r="H479" s="3">
+        <v>31</v>
+      </c>
+      <c r="I479" s="3">
+        <v>37</v>
+      </c>
+      <c r="J479" s="3">
+        <v>27</v>
+      </c>
+      <c r="K479" s="3">
+        <v>22</v>
+      </c>
+      <c r="L479" s="3">
+        <v>9</v>
+      </c>
+      <c r="M479" s="3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="480" spans="1:13">
+      <c r="A480" s="3">
+        <v>1</v>
+      </c>
+      <c r="B480" s="3">
+        <v>66</v>
+      </c>
+      <c r="C480" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="D480" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="E480" s="3">
+        <v>23</v>
+      </c>
+      <c r="F480" s="3">
+        <v>15</v>
+      </c>
+      <c r="G480" s="3">
+        <v>30</v>
+      </c>
+      <c r="H480" s="3">
+        <v>40</v>
+      </c>
+      <c r="I480" s="3">
+        <v>27</v>
+      </c>
+      <c r="J480" s="3">
+        <v>40</v>
+      </c>
+      <c r="K480" s="3">
+        <v>32</v>
+      </c>
+      <c r="L480" s="3">
+        <v>17</v>
+      </c>
+      <c r="M480" s="3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="481" spans="1:13">
+      <c r="A481" s="3">
+        <v>1</v>
+      </c>
+      <c r="B481" s="3">
+        <v>67</v>
+      </c>
+      <c r="C481" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="D481" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="E481" s="3">
+        <v>15</v>
+      </c>
+      <c r="F481" s="3">
+        <v>31</v>
+      </c>
+      <c r="G481" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H481" s="3">
+        <v>29</v>
+      </c>
+      <c r="I481" s="3">
+        <v>31</v>
+      </c>
+      <c r="J481" s="3">
+        <v>37</v>
+      </c>
+      <c r="K481" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L481" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M481" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="482" spans="1:13">
+      <c r="A482" s="3">
+        <v>1</v>
+      </c>
+      <c r="B482" s="3">
+        <v>68</v>
+      </c>
+      <c r="C482" s="3" t="s">
+        <v>650</v>
+      </c>
+      <c r="D482" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="E482" s="3">
+        <v>25</v>
+      </c>
+      <c r="F482" s="3">
         <v>42</v>
       </c>
-      <c r="L458" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="459" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A459" s="1">
+      <c r="G482" s="3">
+        <v>30</v>
+      </c>
+      <c r="H482" s="3">
+        <v>25</v>
+      </c>
+      <c r="I482" s="3">
+        <v>40</v>
+      </c>
+      <c r="J482" s="3">
+        <v>29</v>
+      </c>
+      <c r="K482" s="3">
+        <v>42</v>
+      </c>
+      <c r="L482" s="3">
+        <v>35</v>
+      </c>
+      <c r="M482" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="483" spans="1:13">
+      <c r="A483" s="3">
         <v>1</v>
       </c>
-      <c r="B459" s="1">
+      <c r="B483" s="3">
+        <v>69</v>
+      </c>
+      <c r="C483" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="D483" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="E483" s="3">
+        <v>75</v>
+      </c>
+      <c r="F483" s="3">
+        <v>35</v>
+      </c>
+      <c r="G483" s="3">
+        <v>60</v>
+      </c>
+      <c r="H483" s="3">
+        <v>65</v>
+      </c>
+      <c r="I483" s="3">
+        <v>47</v>
+      </c>
+      <c r="J483" s="3">
+        <v>49</v>
+      </c>
+      <c r="K483" s="3">
+        <v>35</v>
+      </c>
+      <c r="L483" s="3">
+        <v>21</v>
+      </c>
+      <c r="M483" s="3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="484" spans="1:13">
+      <c r="A484" s="3">
+        <v>1</v>
+      </c>
+      <c r="B484" s="3">
+        <v>70</v>
+      </c>
+      <c r="C484" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="D484" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="E484" s="3"/>
+      <c r="F484" s="3"/>
+      <c r="G484" s="3"/>
+      <c r="H484" s="3"/>
+      <c r="I484" s="3"/>
+      <c r="J484" s="3"/>
+      <c r="K484" s="3"/>
+      <c r="L484" s="3"/>
+      <c r="M484" s="3"/>
+    </row>
+    <row r="485" spans="1:13">
+      <c r="A485" s="3">
+        <v>1</v>
+      </c>
+      <c r="B485" s="3">
+        <v>71</v>
+      </c>
+      <c r="C485" s="3" t="s">
+        <v>655</v>
+      </c>
+      <c r="D485" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="E485" s="3">
+        <v>75</v>
+      </c>
+      <c r="F485" s="3">
+        <v>35</v>
+      </c>
+      <c r="G485" s="3">
+        <v>23</v>
+      </c>
+      <c r="H485" s="3">
+        <v>40</v>
+      </c>
+      <c r="I485" s="3">
+        <v>41</v>
+      </c>
+      <c r="J485" s="3">
+        <v>33</v>
+      </c>
+      <c r="K485" s="3">
+        <v>30</v>
+      </c>
+      <c r="L485" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M485" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="486" spans="1:13">
+      <c r="A486" s="3">
+        <v>1</v>
+      </c>
+      <c r="B486" s="3">
+        <v>72</v>
+      </c>
+      <c r="C486" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="D486" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="E486" s="3">
+        <v>79</v>
+      </c>
+      <c r="F486" s="3">
+        <v>40</v>
+      </c>
+      <c r="G486" s="3">
+        <v>75</v>
+      </c>
+      <c r="H486" s="3">
+        <v>61</v>
+      </c>
+      <c r="I486" s="3">
+        <v>39</v>
+      </c>
+      <c r="J486" s="3">
+        <v>47</v>
+      </c>
+      <c r="K486" s="3">
+        <v>50</v>
+      </c>
+      <c r="L486" s="3">
+        <v>65</v>
+      </c>
+      <c r="M486" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="487" spans="1:13">
+      <c r="A487" s="3">
+        <v>1</v>
+      </c>
+      <c r="B487" s="3">
+        <v>73</v>
+      </c>
+      <c r="C487" s="3" t="s">
+        <v>657</v>
+      </c>
+      <c r="D487" s="3" t="s">
+        <v>658</v>
+      </c>
+      <c r="E487" s="3">
+        <v>75</v>
+      </c>
+      <c r="F487" s="3">
+        <v>50</v>
+      </c>
+      <c r="G487" s="3">
+        <v>57</v>
+      </c>
+      <c r="H487" s="3">
+        <v>60</v>
+      </c>
+      <c r="I487" s="3">
+        <v>69</v>
+      </c>
+      <c r="J487" s="3">
+        <v>70</v>
+      </c>
+      <c r="K487" s="3">
+        <v>45</v>
+      </c>
+      <c r="L487" s="3">
+        <v>35</v>
+      </c>
+      <c r="M487" s="3">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="488" spans="1:13">
+      <c r="A488" s="3">
+        <v>1</v>
+      </c>
+      <c r="B488" s="3">
+        <v>74</v>
+      </c>
+      <c r="C488" s="3" t="s">
+        <v>659</v>
+      </c>
+      <c r="D488" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="E488" s="3"/>
+      <c r="F488" s="3"/>
+      <c r="G488" s="3"/>
+      <c r="H488" s="3"/>
+      <c r="I488" s="3"/>
+      <c r="J488" s="3"/>
+      <c r="K488" s="3"/>
+      <c r="L488" s="3"/>
+      <c r="M488" s="3"/>
+    </row>
+    <row r="489" spans="1:13">
+      <c r="A489" s="3">
+        <v>1</v>
+      </c>
+      <c r="B489" s="3">
+        <v>75</v>
+      </c>
+      <c r="C489" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="D489" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="E489" s="3">
+        <v>15</v>
+      </c>
+      <c r="F489" s="3">
+        <v>30</v>
+      </c>
+      <c r="G489" s="3">
+        <v>45</v>
+      </c>
+      <c r="H489" s="3">
+        <v>49</v>
+      </c>
+      <c r="I489" s="3">
+        <v>40</v>
+      </c>
+      <c r="J489" s="3">
+        <v>40</v>
+      </c>
+      <c r="K489" s="3">
+        <v>27</v>
+      </c>
+      <c r="L489" s="3">
+        <v>11</v>
+      </c>
+      <c r="M489" s="3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="490" spans="1:13">
+      <c r="A490" s="3">
+        <v>1</v>
+      </c>
+      <c r="B490" s="3">
+        <v>76</v>
+      </c>
+      <c r="C490" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="D490" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="E490" s="3">
+        <v>19</v>
+      </c>
+      <c r="F490" s="3">
+        <v>35</v>
+      </c>
+      <c r="G490" s="3">
+        <v>15</v>
+      </c>
+      <c r="H490" s="3">
+        <v>40</v>
+      </c>
+      <c r="I490" s="3">
+        <v>31</v>
+      </c>
+      <c r="J490" s="3">
         <v>43</v>
       </c>
-      <c r="L459" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="460" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A460" s="1">
+      <c r="K490" s="3">
+        <v>23</v>
+      </c>
+      <c r="L490" s="3">
+        <v>11</v>
+      </c>
+      <c r="M490" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="491" spans="1:13">
+      <c r="A491" s="3">
         <v>1</v>
       </c>
-      <c r="B460" s="1">
-        <v>44</v>
-      </c>
-      <c r="L460" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="461" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A461" s="1">
+      <c r="B491" s="3">
+        <v>77</v>
+      </c>
+      <c r="C491" s="3" t="s">
+        <v>665</v>
+      </c>
+      <c r="D491" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="E491" s="3"/>
+      <c r="F491" s="3"/>
+      <c r="G491" s="3"/>
+      <c r="H491" s="3"/>
+      <c r="I491" s="3"/>
+      <c r="J491" s="3"/>
+      <c r="K491" s="3"/>
+      <c r="L491" s="3"/>
+      <c r="M491" s="3"/>
+    </row>
+    <row r="492" spans="1:13">
+      <c r="A492" s="3">
         <v>1</v>
       </c>
-      <c r="B461" s="1">
+      <c r="B492" s="3">
+        <v>78</v>
+      </c>
+      <c r="C492" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="D492" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="E492" s="3">
+        <v>57</v>
+      </c>
+      <c r="F492" s="3">
+        <v>32</v>
+      </c>
+      <c r="G492" s="3">
+        <v>23</v>
+      </c>
+      <c r="H492" s="3">
+        <v>37</v>
+      </c>
+      <c r="I492" s="3">
+        <v>35</v>
+      </c>
+      <c r="J492" s="3">
+        <v>39</v>
+      </c>
+      <c r="K492" s="3">
+        <v>23</v>
+      </c>
+      <c r="L492" s="3">
+        <v>22</v>
+      </c>
+      <c r="M492" s="3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="493" spans="1:13">
+      <c r="A493" s="3">
+        <v>1</v>
+      </c>
+      <c r="B493" s="3">
+        <v>79</v>
+      </c>
+      <c r="C493" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D493" s="3" t="s">
+        <v>669</v>
+      </c>
+      <c r="E493" s="3">
+        <v>79</v>
+      </c>
+      <c r="F493" s="3">
+        <v>37</v>
+      </c>
+      <c r="G493" s="3">
+        <v>68</v>
+      </c>
+      <c r="H493" s="3">
+        <v>65</v>
+      </c>
+      <c r="I493" s="3">
+        <v>49</v>
+      </c>
+      <c r="J493" s="3">
+        <v>43</v>
+      </c>
+      <c r="K493" s="3">
+        <v>34</v>
+      </c>
+      <c r="L493" s="3">
+        <v>33</v>
+      </c>
+      <c r="M493" s="3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="494" spans="1:13">
+      <c r="A494" s="3">
+        <v>1</v>
+      </c>
+      <c r="B494" s="3">
+        <v>80</v>
+      </c>
+      <c r="C494" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="D494" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="E494" s="3">
+        <v>79</v>
+      </c>
+      <c r="F494" s="3">
+        <v>40</v>
+      </c>
+      <c r="G494" s="3">
+        <v>59</v>
+      </c>
+      <c r="H494" s="3">
+        <v>51</v>
+      </c>
+      <c r="I494" s="3">
+        <v>47</v>
+      </c>
+      <c r="J494" s="3">
+        <v>51</v>
+      </c>
+      <c r="K494" s="3">
+        <v>43</v>
+      </c>
+      <c r="L494" s="3">
+        <v>51</v>
+      </c>
+      <c r="M494" s="3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="495" spans="1:13">
+      <c r="A495" s="3">
+        <v>1</v>
+      </c>
+      <c r="B495" s="3">
+        <v>81</v>
+      </c>
+      <c r="C495" s="3" t="s">
+        <v>672</v>
+      </c>
+      <c r="D495" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="E495" s="3"/>
+      <c r="F495" s="3"/>
+      <c r="G495" s="3"/>
+      <c r="H495" s="3"/>
+      <c r="I495" s="3"/>
+      <c r="J495" s="3"/>
+      <c r="K495" s="3"/>
+      <c r="L495" s="3"/>
+      <c r="M495" s="3"/>
+    </row>
+    <row r="496" spans="1:13">
+      <c r="A496" s="3">
+        <v>1</v>
+      </c>
+      <c r="B496" s="3">
+        <v>82</v>
+      </c>
+      <c r="C496" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="D496" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="E496" s="3"/>
+      <c r="F496" s="3"/>
+      <c r="G496" s="3"/>
+      <c r="H496" s="3"/>
+      <c r="I496" s="3"/>
+      <c r="J496" s="3"/>
+      <c r="K496" s="3"/>
+      <c r="L496" s="3"/>
+      <c r="M496" s="3"/>
+    </row>
+    <row r="497" spans="1:13">
+      <c r="A497" s="3">
+        <v>1</v>
+      </c>
+      <c r="B497" s="3">
+        <v>83</v>
+      </c>
+      <c r="C497" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="D497" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="E497" s="3">
+        <v>58</v>
+      </c>
+      <c r="F497" s="3">
         <v>45</v>
       </c>
-      <c r="L461" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="462" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A462" s="1">
+      <c r="G497" s="3">
+        <v>40</v>
+      </c>
+      <c r="H497" s="3">
+        <v>35</v>
+      </c>
+      <c r="I497" s="3">
+        <v>50</v>
+      </c>
+      <c r="J497" s="3">
+        <v>45</v>
+      </c>
+      <c r="K497" s="3">
+        <v>35</v>
+      </c>
+      <c r="L497" s="3">
+        <v>35</v>
+      </c>
+      <c r="M497" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="498" spans="1:13">
+      <c r="A498" s="3">
         <v>1</v>
       </c>
-      <c r="B462" s="1">
+      <c r="B498" s="3">
+        <v>84</v>
+      </c>
+      <c r="C498" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="D498" s="3" t="s">
+        <v>677</v>
+      </c>
+      <c r="E498" s="3">
+        <v>75</v>
+      </c>
+      <c r="F498" s="3">
+        <v>30</v>
+      </c>
+      <c r="G498" s="3">
+        <v>39</v>
+      </c>
+      <c r="H498" s="3">
+        <v>42</v>
+      </c>
+      <c r="I498" s="3">
+        <v>41</v>
+      </c>
+      <c r="J498" s="3">
+        <v>37</v>
+      </c>
+      <c r="K498" s="3">
+        <v>26</v>
+      </c>
+      <c r="L498" s="3">
+        <v>25</v>
+      </c>
+      <c r="M498" s="3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="499" spans="1:13">
+      <c r="A499" s="3">
+        <v>1</v>
+      </c>
+      <c r="B499" s="3">
+        <v>85</v>
+      </c>
+      <c r="C499" s="3" t="s">
+        <v>678</v>
+      </c>
+      <c r="D499" s="3"/>
+      <c r="E499" s="3">
+        <v>57</v>
+      </c>
+      <c r="F499" s="3">
+        <v>37</v>
+      </c>
+      <c r="G499" s="3">
+        <v>34</v>
+      </c>
+      <c r="H499" s="3">
+        <v>15</v>
+      </c>
+      <c r="I499" s="3">
+        <v>29</v>
+      </c>
+      <c r="J499" s="3">
+        <v>40</v>
+      </c>
+      <c r="K499" s="3">
+        <v>29</v>
+      </c>
+      <c r="L499" s="3">
+        <v>11</v>
+      </c>
+      <c r="M499" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="500" spans="1:13">
+      <c r="A500" s="3">
+        <v>1</v>
+      </c>
+      <c r="B500" s="3">
+        <v>86</v>
+      </c>
+      <c r="C500" s="3" t="s">
+        <v>679</v>
+      </c>
+      <c r="D500" s="3"/>
+      <c r="E500" s="3">
+        <v>63</v>
+      </c>
+      <c r="F500" s="3">
+        <v>30</v>
+      </c>
+      <c r="G500" s="3">
+        <v>15</v>
+      </c>
+      <c r="H500" s="3">
+        <v>40</v>
+      </c>
+      <c r="I500" s="3">
+        <v>35</v>
+      </c>
+      <c r="J500" s="3">
+        <v>47</v>
+      </c>
+      <c r="K500" s="3">
+        <v>24</v>
+      </c>
+      <c r="L500" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M500" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="501" spans="1:13">
+      <c r="A501" s="3">
+        <v>1</v>
+      </c>
+      <c r="B501" s="3">
+        <v>87</v>
+      </c>
+      <c r="C501" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="D501" s="3"/>
+      <c r="E501" s="3">
+        <v>21</v>
+      </c>
+      <c r="F501" s="3">
+        <v>30</v>
+      </c>
+      <c r="G501" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H501" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I501" s="3">
+        <v>41</v>
+      </c>
+      <c r="J501" s="3">
+        <v>47</v>
+      </c>
+      <c r="K501" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L501" s="3">
         <v>46</v>
       </c>
-      <c r="L462" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="463" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A463" s="1">
+      <c r="M501" s="3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="502" spans="1:13">
+      <c r="A502" s="3">
         <v>1</v>
       </c>
-      <c r="B463" s="1">
+      <c r="B502" s="3">
+        <v>88</v>
+      </c>
+      <c r="C502" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="D502" s="3"/>
+      <c r="E502" s="3">
+        <v>57</v>
+      </c>
+      <c r="F502" s="3">
+        <v>32</v>
+      </c>
+      <c r="G502" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H502" s="3">
+        <v>27</v>
+      </c>
+      <c r="I502" s="3">
+        <v>30</v>
+      </c>
+      <c r="J502" s="3">
+        <v>35</v>
+      </c>
+      <c r="K502" s="3">
+        <v>29</v>
+      </c>
+      <c r="L502" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M502" s="3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="503" spans="1:13">
+      <c r="A503" s="3">
+        <v>1</v>
+      </c>
+      <c r="B503" s="3">
+        <v>89</v>
+      </c>
+      <c r="C503" s="3" t="s">
+        <v>681</v>
+      </c>
+      <c r="D503" s="3"/>
+      <c r="E503" s="3">
+        <v>53</v>
+      </c>
+      <c r="F503" s="3">
+        <v>30</v>
+      </c>
+      <c r="G503" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H503" s="3">
+        <v>30</v>
+      </c>
+      <c r="I503" s="3">
+        <v>40</v>
+      </c>
+      <c r="J503" s="3">
+        <v>31</v>
+      </c>
+      <c r="K503" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L503" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M503" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="504" spans="1:13">
+      <c r="A504" s="3">
+        <v>1</v>
+      </c>
+      <c r="B504" s="3">
+        <v>90</v>
+      </c>
+      <c r="C504" s="3" t="s">
+        <v>682</v>
+      </c>
+      <c r="D504" s="3"/>
+      <c r="E504" s="3">
+        <v>15</v>
+      </c>
+      <c r="F504" s="3">
+        <v>25</v>
+      </c>
+      <c r="G504" s="3">
+        <v>15</v>
+      </c>
+      <c r="H504" s="3">
+        <v>19</v>
+      </c>
+      <c r="I504" s="3">
+        <v>37</v>
+      </c>
+      <c r="J504" s="3">
         <v>47</v>
       </c>
-      <c r="L463" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="464" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A464" s="1">
+      <c r="K504" s="3">
+        <v>37</v>
+      </c>
+      <c r="L504" s="3">
+        <v>11</v>
+      </c>
+      <c r="M504" s="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="505" spans="1:13">
+      <c r="A505" s="3">
         <v>1</v>
       </c>
-      <c r="B464" s="1">
+      <c r="B505" s="3">
+        <v>91</v>
+      </c>
+      <c r="C505" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="D505" s="3"/>
+      <c r="E505" s="3">
+        <v>27</v>
+      </c>
+      <c r="F505" s="3">
+        <v>45</v>
+      </c>
+      <c r="G505" s="3">
+        <v>29</v>
+      </c>
+      <c r="H505" s="3">
+        <v>37</v>
+      </c>
+      <c r="I505" s="3">
+        <v>37</v>
+      </c>
+      <c r="J505" s="3">
+        <v>47</v>
+      </c>
+      <c r="K505" s="3">
+        <v>28</v>
+      </c>
+      <c r="L505" s="3">
         <v>48</v>
       </c>
-      <c r="L464" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="465" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A465" s="1">
+      <c r="M505" s="3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="506" spans="1:13">
+      <c r="A506" s="3">
         <v>1</v>
       </c>
-      <c r="B465" s="1">
-        <v>49</v>
-      </c>
-      <c r="L465" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="466" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A466" s="1">
-        <v>1</v>
-      </c>
-      <c r="B466" s="1">
-        <v>50</v>
-      </c>
-      <c r="L466" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="467" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A467" s="1">
-        <v>1</v>
-      </c>
-      <c r="B467" s="1">
-        <v>51</v>
-      </c>
-      <c r="L467" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="468" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A468" s="1">
-        <v>1</v>
-      </c>
-      <c r="B468" s="1">
-        <v>52</v>
-      </c>
-      <c r="L468" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="469" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A469" s="1">
-        <v>1</v>
-      </c>
-      <c r="B469" s="1">
-        <v>53</v>
-      </c>
-      <c r="L469" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="470" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A470" s="1">
-        <v>1</v>
-      </c>
-      <c r="B470" s="1">
-        <v>54</v>
-      </c>
-      <c r="L470" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="471" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A471" s="1">
-        <v>1</v>
-      </c>
-      <c r="B471" s="1">
-        <v>55</v>
-      </c>
-      <c r="L471" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="472" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A472" s="1">
-        <v>1</v>
-      </c>
-      <c r="B472" s="1">
-        <v>56</v>
-      </c>
-      <c r="L472" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="473" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A473" s="1">
-        <v>1</v>
-      </c>
-      <c r="B473" s="1">
-        <v>57</v>
-      </c>
-      <c r="L473" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="474" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A474" s="1">
-        <v>1</v>
-      </c>
-      <c r="B474" s="1">
-        <v>58</v>
-      </c>
-      <c r="L474" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="475" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A475" s="1">
-        <v>1</v>
-      </c>
-      <c r="B475" s="1">
-        <v>59</v>
-      </c>
-      <c r="L475" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="476" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A476" s="1">
-        <v>1</v>
-      </c>
-      <c r="B476" s="1">
-        <v>60</v>
-      </c>
-      <c r="L476" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="477" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A477" s="1">
-        <v>1</v>
-      </c>
-      <c r="B477" s="1">
-        <v>61</v>
-      </c>
-      <c r="L477" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="478" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A478" s="1">
-        <v>1</v>
-      </c>
-      <c r="B478" s="1">
-        <v>62</v>
-      </c>
-      <c r="L478" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="479" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A479" s="1">
-        <v>1</v>
-      </c>
-      <c r="B479" s="1">
-        <v>63</v>
-      </c>
-      <c r="L479" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="480" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="L480" s="1" t="s">
-        <v>15</v>
+      <c r="B506" s="3">
+        <v>92</v>
+      </c>
+      <c r="C506" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="D506" s="3"/>
+      <c r="E506" s="3">
+        <v>17</v>
+      </c>
+      <c r="F506" s="3">
+        <v>20</v>
+      </c>
+      <c r="G506" s="3">
+        <v>26</v>
+      </c>
+      <c r="H506" s="3">
+        <v>37</v>
+      </c>
+      <c r="I506" s="3">
+        <v>30</v>
+      </c>
+      <c r="J506" s="3">
+        <v>21</v>
+      </c>
+      <c r="K506" s="3">
+        <v>27</v>
+      </c>
+      <c r="L506" s="3">
+        <v>9</v>
+      </c>
+      <c r="M506" s="3">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -17182,7 +20320,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -17191,7 +20329,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
